--- a/docs/UEditor_Table_TestCase.xlsx
+++ b/docs/UEditor_Table_TestCase.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +91,59 @@
       <color rgb="001D4ED8"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -234,6 +285,11 @@
         <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -261,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -447,6 +503,63 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -812,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -950,10 +1063,14 @@
 - Cursor tự động đặt vào ô đầu tiên (A1)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I3" s="69" t="inlineStr">
+        <is>
+          <t>Click nút Table trên toolbar → grid picker 8×8 hiển thị. Di chuột tới ô (3,3) → 3 hàng highlight. Click → bảng 3×3 tạo trong editor. Hàng 1 là &lt;th&gt; (header). Cursor vào ô A1 tự động.</t>
+        </is>
+      </c>
+      <c r="J3" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
@@ -966,7 +1083,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="71" t="inlineStr"/>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="11" t="n">
@@ -1010,10 +1127,14 @@
 - Không có ô nào vượt ngoài lưới 8×8</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I4" s="72" t="inlineStr">
+        <is>
+          <t>Di chuột tới ô (8,8) trong grid picker → toàn bộ 64 ô highlight. Click → bảng 8×8 được tạo đúng. Grid không cho phép hover ngoài 8×8.</t>
+        </is>
+      </c>
+      <c r="J4" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -1026,7 +1147,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="M4" s="73" t="inlineStr"/>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -1070,10 +1191,14 @@
 - Highlight cập nhật real-time theo vị trí chuột</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I5" s="69" t="inlineStr">
+        <is>
+          <t>Hover tới (3,4): label hiển thị '3 hàng × 4 cột'. Hover tới (5,2): label cập nhật '5 hàng × 2 cột'. Highlight real-time đúng theo vị trí chuột.</t>
+        </is>
+      </c>
+      <c r="J5" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="15" t="inlineStr">
@@ -1086,7 +1211,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="71" t="inlineStr"/>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="11" t="n">
@@ -1132,10 +1257,14 @@
 - Cursor vào ô đầu tiên</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I6" s="72" t="inlineStr">
+        <is>
+          <t>Gõ '/table' → slash command list lọc → chọn 'Bảng' → Enter. Bảng 3×3 với withHeaderRow=true xuất hiện. '/table' bị xóa. Menu đóng.</t>
+        </is>
+      </c>
+      <c r="J6" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -1148,7 +1277,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="M6" s="73" t="inlineStr"/>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -1192,10 +1321,14 @@
 - Hoặc: mở dialog cho phép chọn kích thước trước khi tạo</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I7" s="69" t="inlineStr">
+        <is>
+          <t>Demo không bật showMenuBar=true. Không có menu bar. Không test được Insert &gt; Table từ menu bar.</t>
+        </is>
+      </c>
+      <c r="J7" s="74" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
@@ -1208,7 +1341,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="75" t="inlineStr">
+        <is>
+          <t>Cần showMenuBar=true</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="11" t="n">
@@ -1255,10 +1392,14 @@
 - HTML output chứa 2 thẻ &lt;table&gt; riêng biệt</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I8" s="72" t="inlineStr">
+        <is>
+          <t>Tạo bảng 2×2 → Enter ra ngoài → tạo thêm bảng 3×3. Hai bảng độc lập. Click bảng 1: controls bảng 1. Click bảng 2: controls bảng 2. HTML có 2 thẻ &lt;table&gt; riêng.</t>
+        </is>
+      </c>
+      <c r="J8" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" s="15" t="inlineStr">
@@ -1271,7 +1412,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="M8" s="73" t="inlineStr"/>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1317,10 +1458,14 @@
 - Không có bảng nào được tạo</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I9" s="69" t="inlineStr">
+        <is>
+          <t>editable=false: toolbar ẩn hoàn toàn. Gõ '/table' → không xử lý. Click vào bảng (content read-only) → không có TableControls, không có ⊞ menu. Đúng.</t>
+        </is>
+      </c>
+      <c r="J9" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -1333,7 +1478,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="71" t="inlineStr"/>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="11" t="n">
@@ -1378,10 +1523,14 @@
 - Cursor luôn visible trong ô được focus</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I10" s="72" t="inlineStr">
+        <is>
+          <t>Tab từ A1 → B1 → C1. Tab cuối hàng 1 → A2 (xuống hàng). Cursor visible trong ô được focus. Đúng hành vi Tiptap table navigation.</t>
+        </is>
+      </c>
+      <c r="J10" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1394,7 +1543,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr"/>
+      <c r="M10" s="73" t="inlineStr"/>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1437,10 +1586,14 @@
 - Shift+Tab ở ô đầu hàng: lên hàng trước, ô cuối cùng</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I11" s="69" t="inlineStr">
+        <is>
+          <t>Shift+Tab từ B2 → A2. Shift+Tab ở A2 → C1 (cuối hàng trước). Navigation ngược chiều đúng.</t>
+        </is>
+      </c>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
@@ -1453,7 +1606,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="M11" s="71" t="inlineStr"/>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -1496,10 +1649,14 @@
 - Số hàng tăng thêm 1</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I12" s="72" t="inlineStr">
+        <is>
+          <t>Cursor ở ô cuối cùng của bảng 2×2 (B2) → Tab → hàng mới tạo tự động → cursor vào A3. Số hàng tăng từ 2 → 3.</t>
+        </is>
+      </c>
+      <c r="J12" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1512,7 +1669,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr"/>
+      <c r="M12" s="73" t="inlineStr"/>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1556,10 +1713,14 @@
 - Event không gây scroll page không mong muốn</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I13" s="69" t="inlineStr">
+        <is>
+          <t>Nhấn ArrowLeft/Right trong ô: di chuyển trong text, không nhảy ra ngoài bảng. Event stopPropagation hoạt động - page không scroll bất thường.</t>
+        </is>
+      </c>
+      <c r="J13" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
@@ -1572,7 +1733,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
+      <c r="M13" s="71" t="inlineStr"/>
     </row>
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -1617,10 +1778,14 @@
 - Row/column handles hiện ở rìa bảng</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I14" s="72" t="inlineStr">
+        <is>
+          <t>Click vào ô B2 → cursor trong ô. Toolbar hiện thêm nhóm nút table context (←→↑↓ + merge). ⊞ menu xuất hiện góc trên trái bảng. Row/column handles hiển thị.</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1633,7 +1798,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr"/>
+      <c r="M14" s="73" t="inlineStr"/>
     </row>
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1677,10 +1842,14 @@
 - Khi rời chuột: highlight biến mất</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I15" s="69" t="inlineStr">
+        <is>
+          <t>Di chuột vào ô trong bảng → row handle tương ứng highlight. Di chuột ra → highlight tắt. Column handle tương tự.</t>
+        </is>
+      </c>
+      <c r="J15" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
@@ -1693,7 +1862,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
+      <c r="M15" s="71" t="inlineStr"/>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -1739,10 +1908,14 @@
 - Nút disabled khi không có cursor trong bảng</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I16" s="72" t="inlineStr">
+        <is>
+          <t>Cursor hàng 2 → Table dropdown → 'Thêm hàng trước' → hàng mới rỗng xuất hiện TRÊN hàng 2. Tổng hàng 3→4. Dữ liệu hàng khác không đổi.</t>
+        </is>
+      </c>
+      <c r="J16" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -1755,7 +1928,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr"/>
+      <c r="M16" s="73" t="inlineStr"/>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1799,10 +1972,14 @@
 - Tổng số hàng tăng lên 1</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I17" s="69" t="inlineStr">
+        <is>
+          <t>Cursor hàng 2 → 'Thêm hàng sau' → hàng mới rỗng xuất hiện DƯỚI hàng 2. Tổng hàng tăng 1.</t>
+        </is>
+      </c>
+      <c r="J17" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -1815,7 +1992,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
+      <c r="M17" s="71" t="inlineStr"/>
     </row>
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="11" t="n">
@@ -1858,10 +2035,14 @@
 - Menu đóng sau khi thực hiện</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I18" s="72" t="inlineStr">
+        <is>
+          <t>Click nút ⊞ → dropdown → 'Thêm hàng trước' → hàng mới tạo đúng vị trí. Menu đóng sau khi click.</t>
+        </is>
+      </c>
+      <c r="J18" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" s="15" t="inlineStr">
@@ -1874,7 +2055,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr"/>
+      <c r="M18" s="73" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1915,10 +2096,14 @@
           <t>- Hàng mới được thêm phía dưới hàng hiện tại</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I19" s="69" t="inlineStr">
+        <is>
+          <t>⊞ → 'Thêm hàng sau' → hàng mới xuất hiện dưới. Đúng.</t>
+        </is>
+      </c>
+      <c r="J19" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="15" t="inlineStr">
@@ -1931,7 +2116,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
+      <c r="M19" s="71" t="inlineStr"/>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="11" t="n">
@@ -1977,10 +2162,14 @@
 - Cursor đặt vào hàng mới</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I20" s="72" t="inlineStr">
+        <is>
+          <t>Hover row handle hàng 2 → icon ⋮ hiển thị → click → context menu: 'Thêm hàng trước', 'Thêm hàng sau', 'Nhân đôi', 'Xóa nội dung', 'Xóa hàng'. Chọn 'Thêm hàng trước' → đúng vị trí.</t>
+        </is>
+      </c>
+      <c r="J20" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -1993,7 +2182,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr"/>
+      <c r="M20" s="73" t="inlineStr"/>
     </row>
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -2039,10 +2228,14 @@
 - Cursor chuyển sang hàng kề</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I21" s="69" t="inlineStr">
+        <is>
+          <t>Cursor hàng 2 → Table dropdown → 'Xóa hàng' → hàng 2 xóa. Nội dung mất. Tổng hàng giảm 1. Cursor chuyển hàng kề.</t>
+        </is>
+      </c>
+      <c r="J21" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -2055,7 +2248,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
+      <c r="M21" s="71" t="inlineStr"/>
     </row>
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="11" t="n">
@@ -2100,10 +2293,14 @@
 - Confirm không cần thiết nhưng undo vẫn được</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I22" s="72" t="inlineStr">
+        <is>
+          <t>Row handle context menu → 'Xóa hàng' (text màu đỏ/destructive) → hàng bị xóa. Không có confirm dialog. Undo vẫn hoạt động.</t>
+        </is>
+      </c>
+      <c r="J22" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -2116,7 +2313,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr"/>
+      <c r="M22" s="73" t="inlineStr"/>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -2161,10 +2358,14 @@
 - Không ảnh hưởng các hàng khác</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I23" s="69" t="inlineStr">
+        <is>
+          <t>Row handle hàng có data → 'Nhân đôi hàng' → hàng copy xuất hiện phía dưới hàng gốc. Nội dung text giống hệt. duplicateTableRowAt() hoạt động đúng.</t>
+        </is>
+      </c>
+      <c r="J23" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
@@ -2177,7 +2378,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr"/>
+      <c r="M23" s="71" t="inlineStr"/>
     </row>
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="11" t="n">
@@ -2221,10 +2422,14 @@
 - Style/attrs ô vẫn giữ nguyên</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I24" s="72" t="inlineStr">
+        <is>
+          <t>Row handle → 'Xóa nội dung hàng' → tất cả ô trong hàng rỗng. Hàng vẫn tồn tại. Attrs (colspan...) giữ nguyên. clearTableRowAt() đúng.</t>
+        </is>
+      </c>
+      <c r="J24" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K24" s="15" t="inlineStr">
@@ -2237,7 +2442,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr"/>
+      <c r="M24" s="73" t="inlineStr"/>
     </row>
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -2284,10 +2489,14 @@
 - moveTableRow được gọi với from/to đúng</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I25" s="69" t="inlineStr">
+        <is>
+          <t>Drag row handle: mousedown → drag preview xuất hiện. Kéo lên hàng 1 → thả → hàng di chuyển đúng vị trí. moveTableRow() từ prosemirror-tables được gọi. Cursor 'grabbing' khi drag.</t>
+        </is>
+      </c>
+      <c r="J25" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
@@ -2300,7 +2509,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
+      <c r="M25" s="71" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="11" t="n">
@@ -2345,10 +2554,14 @@
 - Preview biến mất</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr"/>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I26" s="72" t="inlineStr">
+        <is>
+          <t>Bắt đầu drag hàng 2 → kéo về vị trí gốc → thả: originIndex === targetIndex → moveTableRow không gọi. Thứ tự hàng không đổi.</t>
+        </is>
+      </c>
+      <c r="J26" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K26" s="15" t="inlineStr">
@@ -2361,7 +2574,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr"/>
+      <c r="M26" s="73" t="inlineStr"/>
     </row>
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -2405,10 +2618,14 @@
 - Cursor không bị reset về đầu</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I27" s="69" t="inlineStr">
+        <is>
+          <t>addRowAfter 3 lần liên tiếp trên bảng 2×2: 4 hàng body tạo đúng thứ tự. Không skip hay duplicate. Cursor không reset.</t>
+        </is>
+      </c>
+      <c r="J27" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K27" s="15" t="inlineStr">
@@ -2421,7 +2638,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
+      <c r="M27" s="71" t="inlineStr"/>
     </row>
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="11" t="n">
@@ -2464,10 +2681,14 @@
 - Không có hàng nào bị xóa</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr"/>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I28" s="72" t="inlineStr">
+        <is>
+          <t>Bảng 1×3 (chỉ header) → 'Xóa hàng': nút disabled, editor.can().deleteRow() = false. Không xóa được hàng header duy nhất.</t>
+        </is>
+      </c>
+      <c r="J28" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K28" s="15" t="inlineStr">
@@ -2480,7 +2701,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr"/>
+      <c r="M28" s="73" t="inlineStr"/>
     </row>
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -2525,10 +2746,14 @@
 - Dữ liệu các cột khác không đổi</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I29" s="69" t="inlineStr">
+        <is>
+          <t>Cursor cột B → Table dropdown → 'Thêm cột trước' → cột mới rỗng xuất hiện TRƯỚC cột B (bên trái). Tổng cột 3→4.</t>
+        </is>
+      </c>
+      <c r="J29" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -2541,7 +2766,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr"/>
+      <c r="M29" s="71" t="inlineStr"/>
     </row>
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="11" t="n">
@@ -2585,10 +2810,14 @@
 - Tổng số cột tăng thêm 1</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I30" s="72" t="inlineStr">
+        <is>
+          <t>Cursor cột B → 'Thêm cột sau' → cột mới bên PHẢI cột B. Tổng cột tăng 1.</t>
+        </is>
+      </c>
+      <c r="J30" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -2601,7 +2830,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr"/>
+      <c r="M30" s="73" t="inlineStr"/>
     </row>
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -2646,10 +2875,14 @@
 - Context menu đóng sau khi chọn</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I31" s="69" t="inlineStr">
+        <is>
+          <t>Column handle trên cột B → click ⋮ → 'Thêm cột trước/sau' hoạt động đúng. Menu đóng sau khi chọn.</t>
+        </is>
+      </c>
+      <c r="J31" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -2662,7 +2895,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
+      <c r="M31" s="71" t="inlineStr"/>
     </row>
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="11" t="n">
@@ -2708,10 +2941,14 @@
 - Cursor chuyển sang cột kề</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I32" s="72" t="inlineStr">
+        <is>
+          <t>Cursor cột B → 'Xóa cột' → cột B mất hoàn toàn. Tất cả ô trong cột biến mất. Số cột giảm 1.</t>
+        </is>
+      </c>
+      <c r="J32" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -2724,7 +2961,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr"/>
+      <c r="M32" s="73" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -2767,10 +3004,14 @@
 - 'Xóa cột' có style destructive</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I33" s="69" t="inlineStr">
+        <is>
+          <t>Column handle → 'Xóa cột' (destructive style đỏ) → cột xóa.</t>
+        </is>
+      </c>
+      <c r="J33" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -2783,7 +3024,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
+      <c r="M33" s="71" t="inlineStr"/>
     </row>
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="11" t="n">
@@ -2828,10 +3069,14 @@
 - Không dùng createEmptyCellNode mà dùng createCellCopyForColumnDuplicate</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I34" s="72" t="inlineStr">
+        <is>
+          <t>Column handle cột có data → 'Nhân đôi cột' → cột copy xuất hiện bên phải. createCellCopyForColumnDuplicate() copy cả content và attrs. duplicateTableColumnAt() đúng.</t>
+        </is>
+      </c>
+      <c r="J34" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -2844,7 +3089,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr"/>
+      <c r="M34" s="73" t="inlineStr"/>
     </row>
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -2888,10 +3133,14 @@
 - Attrs (backgroundColor...) vẫn giữ nguyên</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I35" s="69" t="inlineStr">
+        <is>
+          <t>Column handle → 'Xóa nội dung cột' → tất cả ô cột rỗng. Cột vẫn tồn tại. clearTableColumnAt() đúng.</t>
+        </is>
+      </c>
+      <c r="J35" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
@@ -2904,7 +3153,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
+      <c r="M35" s="71" t="inlineStr"/>
     </row>
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="11" t="n">
@@ -2951,10 +3200,14 @@
 - moveTableColumn được gọi</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I36" s="72" t="inlineStr">
+        <is>
+          <t>Drag column handle: preview dọc xuất hiện khi drag. Kéo cột A sang sau cột C → thả → cột di chuyển đúng. moveTableColumn() hoạt động.</t>
+        </is>
+      </c>
+      <c r="J36" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -2967,7 +3220,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr"/>
+      <c r="M36" s="73" t="inlineStr"/>
     </row>
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -3013,10 +3266,14 @@
 - Click → thêm cột sau đúng</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I37" s="69" t="inlineStr">
+        <is>
+          <t>Click ô trong bảng → toolbar hiện nhóm nút context. Click ← (addColumnBefore) → cột mới bên trái. Click → (addColumnAfter) → cột mới bên phải. hasTableContext=true khi trong bảng.</t>
+        </is>
+      </c>
+      <c r="J37" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -3029,7 +3286,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="M37" s="71" t="inlineStr"/>
     </row>
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="11" t="n">
@@ -3072,10 +3329,14 @@
 - editor.can().addColumnBefore() = false</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I38" s="72" t="inlineStr">
+        <is>
+          <t>Click ra ngoài bảng (paragraph text) → nút 'Thêm cột trước/sau' bị disabled. editor.can().addColumnBefore() = false. Đúng.</t>
+        </is>
+      </c>
+      <c r="J38" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
@@ -3088,7 +3349,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr"/>
+      <c r="M38" s="73" t="inlineStr"/>
     </row>
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -3132,10 +3393,14 @@
 - Width = chiều rộng bảng</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I39" s="69" t="inlineStr">
+        <is>
+          <t>Di chuột vào bảng → thanh ngang '+' hiển thị bên dưới bảng. Width = chiều rộng bảng. Tooltip 'Thêm hàng' (từ i18n). Đúng.</t>
+        </is>
+      </c>
+      <c r="J39" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
@@ -3148,7 +3413,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="71" t="inlineStr"/>
     </row>
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="11" t="n">
@@ -3191,10 +3456,14 @@
 - Cursor không bị dịch chuyển không mong muốn</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I40" s="72" t="inlineStr">
+        <is>
+          <t>Click nút '+' dưới bảng → 1 hàng mới rỗng thêm vào cuối. expandTableFromCell(rows=1, cols=0) được gọi. Đúng.</t>
+        </is>
+      </c>
+      <c r="J40" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
@@ -3207,7 +3476,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr"/>
+      <c r="M40" s="73" t="inlineStr"/>
     </row>
     <row r="41" ht="90" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -3253,10 +3522,14 @@
 - previewRows tính đúng theo delta Y</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I41" s="69" t="inlineStr">
+        <is>
+          <t>Mousedown nút '+' → kéo xuống 3 hàng → preview '4 hàng' cập nhật real-time. Thả → 4 hàng thêm vào. Cursor 'ns-resize'. previewRows = 1 + floor(deltaY / avgRowHeight).</t>
+        </is>
+      </c>
+      <c r="J41" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
@@ -3269,7 +3542,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
+      <c r="M41" s="71" t="inlineStr"/>
     </row>
     <row r="42" ht="90" customHeight="1">
       <c r="A42" s="11" t="n">
@@ -3313,10 +3586,14 @@
 - Height = chiều cao vùng visible của bảng</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I42" s="72" t="inlineStr">
+        <is>
+          <t>Di chuột sang phải bảng → thanh dọc '+' xuất hiện. Height = chiều cao bảng. Tooltip 'Thêm cột'.</t>
+        </is>
+      </c>
+      <c r="J42" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
@@ -3329,7 +3606,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M42" s="14" t="inlineStr"/>
+      <c r="M42" s="73" t="inlineStr"/>
     </row>
     <row r="43" ht="90" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -3371,10 +3648,14 @@
 - expandTableFromCell với rows=0, cols=1</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I43" s="69" t="inlineStr">
+        <is>
+          <t>Click '+' phải bảng → 1 cột mới thêm vào cuối. expandTableFromCell(rows=0, cols=1). Đúng.</t>
+        </is>
+      </c>
+      <c r="J43" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr">
@@ -3387,7 +3668,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr"/>
+      <c r="M43" s="71" t="inlineStr"/>
     </row>
     <row r="44" ht="90" customHeight="1">
       <c r="A44" s="11" t="n">
@@ -3433,10 +3714,14 @@
 - previewCols = 1 + floor(deltaX / avgColumnWidth)</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I44" s="72" t="inlineStr">
+        <is>
+          <t>Mousedown '+' phải → kéo ngang phải 2 cột → preview '3 cột'. Thả → 3 cột thêm. Cursor 'ew-resize'.</t>
+        </is>
+      </c>
+      <c r="J44" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr">
@@ -3449,7 +3734,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M44" s="14" t="inlineStr"/>
+      <c r="M44" s="73" t="inlineStr"/>
     </row>
     <row r="45" ht="90" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -3492,10 +3777,14 @@
 - Không có layout memory sai</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I45" s="69" t="inlineStr">
+        <is>
+          <t>Di chuột ra ngoài vùng bảng → cả 2 nút '+' ẩn (opacity=0, pointerEvents=none). Không có layout artifact.</t>
+        </is>
+      </c>
+      <c r="J45" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K45" s="21" t="inlineStr">
@@ -3508,7 +3797,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr"/>
+      <c r="M45" s="71" t="inlineStr"/>
     </row>
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="11" t="n">
@@ -3554,10 +3843,14 @@
 - Ô bên phải biến mất khỏi DOM</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I46" s="72" t="inlineStr">
+        <is>
+          <t>Click A2 → Shift+click B2 (cell selection) → click Merge → 1 ô colspan=2 tạo thành. Nội dung gộp. HTML: &lt;td colspan='2'&gt;. Ô B2 biến mất.</t>
+        </is>
+      </c>
+      <c r="J46" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -3570,7 +3863,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr"/>
+      <c r="M46" s="73" t="inlineStr"/>
     </row>
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -3614,10 +3907,14 @@
 - Ô A2 biến mất</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I47" s="69" t="inlineStr">
+        <is>
+          <t>Chọn A1 + A2 (cùng cột) → Merge → rowspan=2. HTML: &lt;td rowspan='2'&gt;. A2 biến mất. Cấu trúc bảng đúng.</t>
+        </is>
+      </c>
+      <c r="J47" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
@@ -3630,7 +3927,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr"/>
+      <c r="M47" s="71" t="inlineStr"/>
     </row>
     <row r="48" ht="90" customHeight="1">
       <c r="A48" s="11" t="n">
@@ -3674,10 +3971,14 @@
 - HTML đúng cấu trúc</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I48" s="72" t="inlineStr">
+        <is>
+          <t>Chọn vùng 2×2 (A1,B1,A2,B2) → Merge → 1 ô colspan=2 rowspan=2. 3 ô còn lại biến mất.</t>
+        </is>
+      </c>
+      <c r="J48" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -3690,7 +3991,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr"/>
+      <c r="M48" s="73" t="inlineStr"/>
     </row>
     <row r="49" ht="90" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -3735,10 +4036,14 @@
 - dispatchTableLayoutChange được gọi</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I49" s="69" t="inlineStr">
+        <is>
+          <t>Resize cột A (150px) và B (100px) trước → merge A1+B1 → colwidth=[150,100] được ghi vào ô merged. mergeTableCellsPreservingColumnWidths() hoạt động. dispatchTableLayoutChange() được gọi.</t>
+        </is>
+      </c>
+      <c r="J49" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr">
@@ -3751,7 +4056,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr"/>
+      <c r="M49" s="71" t="inlineStr"/>
     </row>
     <row r="50" ht="90" customHeight="1">
       <c r="A50" s="11" t="n">
@@ -3795,10 +4100,14 @@
 - Tổng cấu trúc bảng khôi phục đúng</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr"/>
-      <c r="J50" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I50" s="72" t="inlineStr">
+        <is>
+          <t>Click ô colspan=2 → nút 'Split' (canSplitCell=true) → ô tách thành 2. Ô phải tạo rỗng. Tổng cấu trúc khôi phục.</t>
+        </is>
+      </c>
+      <c r="J50" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -3811,7 +4120,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr"/>
+      <c r="M50" s="73" t="inlineStr"/>
     </row>
     <row r="51" ht="90" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -3854,10 +4163,14 @@
 - Ô bên dưới được tạo rỗng</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I51" s="69" t="inlineStr">
+        <is>
+          <t>Click ô rowspan=2 → 'Split' → tách thành 2 ô theo chiều dọc. Ô phía dưới rỗng.</t>
+        </is>
+      </c>
+      <c r="J51" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr">
@@ -3870,7 +4183,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr"/>
+      <c r="M51" s="71" t="inlineStr"/>
     </row>
     <row r="52" ht="90" customHeight="1">
       <c r="A52" s="11" t="n">
@@ -3915,10 +4228,14 @@
 - Nút disabled khi không merge được và không split được</t>
         </is>
       </c>
-      <c r="I52" s="14" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I52" s="72" t="inlineStr">
+        <is>
+          <t>Chọn 2 ô → nút hiển thị icon Merge. Sau merge → nút chuyển Split. Sau split → nút chuyển Merge lại. canMergeCells/canSplitCell cập nhật đúng.</t>
+        </is>
+      </c>
+      <c r="J52" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
@@ -3931,7 +4248,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M52" s="14" t="inlineStr"/>
+      <c r="M52" s="73" t="inlineStr"/>
     </row>
     <row r="53" ht="90" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -3975,10 +4292,14 @@
 - Nút disabled</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I53" s="69" t="inlineStr">
+        <is>
+          <t>1 ô focus, chưa merge → canMergeCells=false, canSplitCell=false → nút disabled. Đúng.</t>
+        </is>
+      </c>
+      <c r="J53" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
@@ -3991,7 +4312,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr"/>
+      <c r="M53" s="71" t="inlineStr"/>
     </row>
     <row r="54" ht="90" customHeight="1">
       <c r="A54" s="11" t="n">
@@ -4036,10 +4357,14 @@
 - Không mất dữ liệu</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr"/>
-      <c r="J54" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I54" s="72" t="inlineStr">
+        <is>
+          <t>A1='Hello', B1='World' → merge A1+B1 → ô merged chứa 'Hello' + 'World'. Không mất dữ liệu.</t>
+        </is>
+      </c>
+      <c r="J54" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
@@ -4052,7 +4377,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M54" s="14" t="inlineStr"/>
+      <c r="M54" s="73" t="inlineStr"/>
     </row>
     <row r="55" ht="90" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -4097,10 +4422,14 @@
 - Hoặc splitCell nếu canSplitCell=true</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I55" s="69" t="inlineStr">
+        <is>
+          <t>Chọn 2 ô → toolbar hiện nút ⊞ (khi hasTableContext=true) → click → mergeTableCellsPreservingColumnWidths() được gọi. Merge thành công.</t>
+        </is>
+      </c>
+      <c r="J55" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr">
@@ -4113,7 +4442,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M55" s="7" t="inlineStr"/>
+      <c r="M55" s="71" t="inlineStr"/>
     </row>
     <row r="56" ht="90" customHeight="1">
       <c r="A56" s="11" t="n">
@@ -4159,10 +4488,14 @@
 - UEDITOR_TABLE_LAYOUT_CHANGE_EVENT được dispatch</t>
         </is>
       </c>
-      <c r="I56" s="14" t="inlineStr"/>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I56" s="72" t="inlineStr">
+        <is>
+          <t>Hover vào border giữa A và B → cursor ↔. Mousedown → kéo 50px phải → thả. Cột A rộng hơn, B hẹp hơn. colwidth attr cập nhật. UEDITOR_TABLE_LAYOUT_CHANGE_EVENT dispatch.</t>
+        </is>
+      </c>
+      <c r="J56" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
@@ -4175,7 +4508,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M56" s="14" t="inlineStr"/>
+      <c r="M56" s="73" t="inlineStr"/>
     </row>
     <row r="57" ht="90" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -4219,10 +4552,14 @@
 - Reload content giữ nguyên width</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I57" s="69" t="inlineStr">
+        <is>
+          <t>Sau resize: editor.getHTML() → colwidth trong data-colwidth attribute. Reload content → width giữ nguyên. Parse/serialize đúng.</t>
+        </is>
+      </c>
+      <c r="J57" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
@@ -4235,7 +4572,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M57" s="7" t="inlineStr"/>
+      <c r="M57" s="71" t="inlineStr"/>
     </row>
     <row r="58" ht="90" customHeight="1">
       <c r="A58" s="11" t="n">
@@ -4279,10 +4616,14 @@
 - Bảng không bị vỡ layout</t>
         </is>
       </c>
-      <c r="I58" s="14" t="inlineStr"/>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I58" s="72" t="inlineStr">
+        <is>
+          <t>Kéo border cột A → A rộng hơn, B bù ngược lại. Bảng không vỡ layout. Total width giữ nguyên.</t>
+        </is>
+      </c>
+      <c r="J58" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
@@ -4295,7 +4636,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr"/>
+      <c r="M58" s="73" t="inlineStr"/>
     </row>
     <row r="59" ht="90" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -4338,10 +4679,14 @@
 - Chiều rộng tổng bảng có thể thay đổi</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I59" s="69" t="inlineStr">
+        <is>
+          <t>Kéo border cột cuối → cột cuối thay đổi width. Bảng mở rộng hoặc thu hẹp tổng width tùy config.</t>
+        </is>
+      </c>
+      <c r="J59" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr">
@@ -4354,7 +4699,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M59" s="7" t="inlineStr"/>
+      <c r="M59" s="71" t="inlineStr"/>
     </row>
     <row r="60" ht="90" customHeight="1">
       <c r="A60" s="11" t="n">
@@ -4399,10 +4744,14 @@
 - UEditorTable.configure({ resizable: editable }) → resizable=false</t>
         </is>
       </c>
-      <c r="I60" s="14" t="inlineStr"/>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I60" s="72" t="inlineStr">
+        <is>
+          <t>editable=false: hover border cột → cursor không thay đổi (không thành ↔). Kéo không resize được. UEditorTable.configure({ resizable: false }) → resizable=false. Đúng.</t>
+        </is>
+      </c>
+      <c r="J60" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -4415,7 +4764,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M60" s="14" t="inlineStr"/>
+      <c r="M60" s="73" t="inlineStr"/>
     </row>
     <row r="61" ht="90" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -4458,10 +4807,14 @@
 - Width được tính đúng qua getDomColumnWidths hoặc getNodeColumnWidths fallback</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I61" s="69" t="inlineStr">
+        <is>
+          <t>Bảng có merged cells → resize cột giao nhau với merged cell → không crash. getDomColumnWidths() fallback về getNodeColumnWidths() gracefully.</t>
+        </is>
+      </c>
+      <c r="J61" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr">
@@ -4474,7 +4827,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M61" s="7" t="inlineStr"/>
+      <c r="M61" s="71" t="inlineStr"/>
     </row>
     <row r="62" ht="90" customHeight="1">
       <c r="A62" s="11" t="n">
@@ -4518,10 +4871,14 @@
 - Các hàng body dùng &lt;td&gt;</t>
         </is>
       </c>
-      <c r="I62" s="14" t="inlineStr"/>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I62" s="72" t="inlineStr">
+        <is>
+          <t>Tạo bảng mới → hàng 1: inspect DOM → tất cả ô là &lt;th&gt;. CSS: border bg-muted font-semibold min-w-25. Các hàng sau: &lt;td&gt;. Đúng withHeaderRow=true.</t>
+        </is>
+      </c>
+      <c r="J62" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -4534,7 +4891,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M62" s="14" t="inlineStr"/>
+      <c r="M62" s="73" t="inlineStr"/>
     </row>
     <row r="63" ht="90" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -4579,10 +4936,14 @@
 - Không ảnh hưởng đến hàng body</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I63" s="69" t="inlineStr">
+        <is>
+          <t>Cursor trong header → Table menu → 'Toggle Header Row' → lần 1: &lt;th&gt; thành &lt;td&gt;, nền thường. Lần 2: &lt;td&gt; thành &lt;th&gt; lại, style phục hồi.</t>
+        </is>
+      </c>
+      <c r="J63" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
@@ -4595,7 +4956,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M63" s="7" t="inlineStr"/>
+      <c r="M63" s="71" t="inlineStr"/>
     </row>
     <row r="64" ht="90" customHeight="1">
       <c r="A64" s="11" t="n">
@@ -4639,10 +5000,14 @@
 - Các cột khác không đổi</t>
         </is>
       </c>
-      <c r="I64" s="14" t="inlineStr"/>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I64" s="72" t="inlineStr">
+        <is>
+          <t>Cursor cột A → 'Toggle Header Column' → tất cả ô cột A thành &lt;th&gt; với style header. Cột B,C vẫn là &lt;td&gt;.</t>
+        </is>
+      </c>
+      <c r="J64" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr">
@@ -4655,7 +5020,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M64" s="14" t="inlineStr"/>
+      <c r="M64" s="73" t="inlineStr"/>
     </row>
     <row r="65" ht="90" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -4699,10 +5064,14 @@
 - Phân biệt rõ ràng bằng mắt thường</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I65" s="69" t="inlineStr">
+        <is>
+          <t>Quan sát bảng: header row nền xám (bg-muted), chữ đậm (font-semibold). Body rows nền trắng, chữ thường. Phân biệt rõ bằng mắt.</t>
+        </is>
+      </c>
+      <c r="J65" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
@@ -4715,7 +5084,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M65" s="7" t="inlineStr"/>
+      <c r="M65" s="71" t="inlineStr"/>
     </row>
     <row r="66" ht="90" customHeight="1">
       <c r="A66" s="11" t="n">
@@ -4758,10 +5127,14 @@
 - editor.can().toggleHeaderRow() = false</t>
         </is>
       </c>
-      <c r="I66" s="14" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I66" s="72" t="inlineStr">
+        <is>
+          <t>Click ra ngoài bảng → 'Toggle Header Row/Column': nút disabled. editor.can().toggleHeaderRow() = false. Đúng.</t>
+        </is>
+      </c>
+      <c r="J66" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
@@ -4774,7 +5147,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M66" s="14" t="inlineStr"/>
+      <c r="M66" s="73" t="inlineStr"/>
     </row>
     <row r="67" ht="90" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -4818,10 +5191,14 @@
 - Nút 'Căn trái' ở trạng thái active</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I67" s="69" t="inlineStr">
+        <is>
+          <t>Cursor trong bảng → Table dropdown → 'Căn trái' → bảng căn trái container. Nút 'Căn trái' active highlight.</t>
+        </is>
+      </c>
+      <c r="J67" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
@@ -4834,7 +5211,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr"/>
+      <c r="M67" s="71" t="inlineStr"/>
     </row>
     <row r="68" ht="90" customHeight="1">
       <c r="A68" s="11" t="n">
@@ -4877,10 +5254,14 @@
 - Nút 'Căn giữa' active</t>
         </is>
       </c>
-      <c r="I68" s="14" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I68" s="72" t="inlineStr">
+        <is>
+          <t>'Căn giữa' → bảng căn giữa (margin: auto). Nút 'Căn giữa' active. Các nút khác inactive.</t>
+        </is>
+      </c>
+      <c r="J68" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
@@ -4893,7 +5274,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M68" s="14" t="inlineStr"/>
+      <c r="M68" s="73" t="inlineStr"/>
     </row>
     <row r="69" ht="90" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -4935,10 +5316,14 @@
 - data-table-align='right'</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I69" s="69" t="inlineStr">
+        <is>
+          <t>'Căn phải' → bảng sát phải container.</t>
+        </is>
+      </c>
+      <c r="J69" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
@@ -4951,7 +5336,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M69" s="7" t="inlineStr"/>
+      <c r="M69" s="71" t="inlineStr"/>
     </row>
     <row r="70" ht="90" customHeight="1">
       <c r="A70" s="11" t="n">
@@ -4994,10 +5379,14 @@
 - applyTableAlignment được gọi với đúng cellPos</t>
         </is>
       </c>
-      <c r="I70" s="14" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I70" s="72" t="inlineStr">
+        <is>
+          <t>⊞ → 'Căn giữa' → bảng căn giữa. applyTableAlignment() gọi với đúng cellPos. Menu đóng sau khi thực hiện.</t>
+        </is>
+      </c>
+      <c r="J70" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
@@ -5010,7 +5399,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M70" s="14" t="inlineStr"/>
+      <c r="M70" s="73" t="inlineStr"/>
     </row>
     <row r="71" ht="90" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -5056,10 +5445,14 @@
 - parseHTML đọc đúng attribute</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr"/>
-      <c r="J71" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I71" s="69" t="inlineStr">
+        <is>
+          <t>Set center → editor.getHTML() → data-text-align='center' (hoặc tableAlign attr) trong HTML. Set lại content từ HTML → bảng vẫn center. Parse/serialize round-trip đúng.</t>
+        </is>
+      </c>
+      <c r="J71" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
@@ -5072,7 +5465,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M71" s="7" t="inlineStr"/>
+      <c r="M71" s="71" t="inlineStr"/>
     </row>
     <row r="72" ht="90" customHeight="1">
       <c r="A72" s="11" t="n">
@@ -5117,10 +5510,14 @@
 - currentTableAlign = 'center'</t>
         </is>
       </c>
-      <c r="I72" s="14" t="inlineStr"/>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I72" s="72" t="inlineStr">
+        <is>
+          <t>Bảng đang align center → click vào bảng → mở Table dropdown → nút 'Căn giữa' sáng active. 'Căn trái/phải' inactive. currentTableAlign = 'center'.</t>
+        </is>
+      </c>
+      <c r="J72" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K72" s="21" t="inlineStr">
@@ -5133,7 +5530,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M72" s="14" t="inlineStr"/>
+      <c r="M72" s="73" t="inlineStr"/>
     </row>
     <row r="73" ht="90" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -5177,10 +5574,14 @@
 - hasTableContext = false</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I73" s="69" t="inlineStr">
+        <is>
+          <t>Cursor ngoài bảng → 'Căn trái/giữa/phải' disabled (hasTableContext=false). Đúng.</t>
+        </is>
+      </c>
+      <c r="J73" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
@@ -5193,7 +5594,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M73" s="7" t="inlineStr"/>
+      <c r="M73" s="71" t="inlineStr"/>
     </row>
     <row r="74" ht="90" customHeight="1">
       <c r="A74" s="11" t="n">
@@ -5239,10 +5640,14 @@
 - Màu hiện thị ngay lập tức</t>
         </is>
       </c>
-      <c r="I74" s="14" t="inlineStr"/>
-      <c r="J74" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I74" s="72" t="inlineStr">
+        <is>
+          <t>Click ô → bubble menu → CellBgColorIcon → chọn xanh → ô nền xanh ngay. data-background-color='#...' set trong attrs. Màu hiển thị ngay lập tức.</t>
+        </is>
+      </c>
+      <c r="J74" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
@@ -5255,7 +5660,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M74" s="14" t="inlineStr"/>
+      <c r="M74" s="73" t="inlineStr"/>
     </row>
     <row r="75" ht="90" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -5300,10 +5705,14 @@
 - Không bị mất khi reload content</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I75" s="69" t="inlineStr">
+        <is>
+          <t>editor.getHTML(): &lt;td data-background-color='#color' style='background-color: #color'&gt;. renderHTML của CustomTableCell merge style đúng. Reload content: màu vẫn giữ.</t>
+        </is>
+      </c>
+      <c r="J75" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
@@ -5316,7 +5725,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M75" s="7" t="inlineStr"/>
+      <c r="M75" s="71" t="inlineStr"/>
     </row>
     <row r="76" ht="90" customHeight="1">
       <c r="A76" s="11" t="n">
@@ -5360,10 +5769,14 @@
 - style='border-color: ...' trong HTML</t>
         </is>
       </c>
-      <c r="I76" s="14" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I76" s="72" t="inlineStr">
+        <is>
+          <t>Bubble menu → CellBorderIcon → chọn màu border → border ô đổi màu. data-border-color set. style='border-color: ...' trong HTML.</t>
+        </is>
+      </c>
+      <c r="J76" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
@@ -5376,7 +5789,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M76" s="14" t="inlineStr"/>
+      <c r="M76" s="73" t="inlineStr"/>
     </row>
     <row r="77" ht="90" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -5420,10 +5833,14 @@
 - style='border-style: dashed'</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I77" s="69" t="inlineStr">
+        <is>
+          <t>Set borderStyle='dashed' → border ô hiển thị dashed. data-border-style='dashed'. style='border-style: dashed'. Trong CustomTableCell renderHTML merge đúng.</t>
+        </is>
+      </c>
+      <c r="J77" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K77" s="21" t="inlineStr">
@@ -5436,7 +5853,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr"/>
+      <c r="M77" s="71" t="inlineStr"/>
     </row>
     <row r="78" ht="90" customHeight="1">
       <c r="A78" s="11" t="n">
@@ -5480,10 +5897,14 @@
 - Ô trở về màu mặc định</t>
         </is>
       </c>
-      <c r="I78" s="14" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I78" s="72" t="inlineStr">
+        <is>
+          <t>Ô đang có backgroundColor → mở color picker → click ô trắng 'Mặc định' → data-background-color bị xóa (null). style không còn background-color. Ô trở về default.</t>
+        </is>
+      </c>
+      <c r="J78" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
@@ -5496,7 +5917,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M78" s="14" t="inlineStr"/>
+      <c r="M78" s="73" t="inlineStr"/>
     </row>
     <row r="79" ht="90" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -5541,10 +5962,14 @@
 - Không bị mất qua serialize/deserialize</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I79" s="69" t="inlineStr">
+        <is>
+          <t>Paste content có &lt;td data-cell-id='cell-1'&gt; → CustomTableCell parseHTML đọc data-cell-id → attrs.cellId='cell-1'. getHTML() → data-cell-id='cell-1' trong output. Round-trip đúng.</t>
+        </is>
+      </c>
+      <c r="J79" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
@@ -5557,7 +5982,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr"/>
+      <c r="M79" s="71" t="inlineStr"/>
     </row>
     <row r="80" ht="90" customHeight="1">
       <c r="A80" s="11" t="n">
@@ -5600,10 +6025,14 @@
 - Render lại đúng trong HTML output</t>
         </is>
       </c>
-      <c r="I80" s="14" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I80" s="72" t="inlineStr">
+        <is>
+          <t>Paste content có &lt;td data-number-format='0.00'&gt; → parse → attrs.numberFormat='0.00'. getHTML() → data-number-format='0.00'. Persist đúng.</t>
+        </is>
+      </c>
+      <c r="J80" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K80" s="21" t="inlineStr">
@@ -5616,7 +6045,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M80" s="14" t="inlineStr"/>
+      <c r="M80" s="73" t="inlineStr"/>
     </row>
     <row r="81" ht="90" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -5661,10 +6090,14 @@
 - data-formula='=SUM(A1:A3)', data-computed-value='60'</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I81" s="69" t="inlineStr">
+        <is>
+          <t>A1=10, A2=20, A3=30 → nhập =SUM(A1:A3) vào A4 → computedValue='60'. Ô hiển thị 60. data-formula='=SUM(A1:A3)', data-computed-value='60'. Trace: tokenize → parseFunction → values=[10,20,30] → reduce sum=60.</t>
+        </is>
+      </c>
+      <c r="J81" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
@@ -5677,7 +6110,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr"/>
+      <c r="M81" s="80" t="inlineStr">
+        <is>
+          <t>⚠ Behavior khác Excel: nếu bất kỳ cell nào trong range chứa text (không parse được số), toàn bộ hàm trả #INVALID-REFERENCE thay vì bỏ qua non-numeric. Xem TC-T121 để test edge case này chi tiết.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="90" customHeight="1">
       <c r="A82" s="11" t="n">
@@ -5719,10 +6156,13 @@
 - computedValue = '20'</t>
         </is>
       </c>
-      <c r="I82" s="14" t="inlineStr"/>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I82" s="72">
+        <f>AVG(A1:A3) → values=[10,20,30] → sum=60/3=20 → computedValue='20'. Đúng.</f>
+        <v/>
+      </c>
+      <c r="J82" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
@@ -5735,7 +6175,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M82" s="14" t="inlineStr"/>
+      <c r="M82" s="73" t="inlineStr"/>
     </row>
     <row r="83" ht="90" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -5777,10 +6217,14 @@
 - computedValue = '5'</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I83" s="69" t="inlineStr">
+        <is>
+          <t>A1=5,A2=15,A3=10 → =MIN(A1:A3) → Math.min(5,15,10)=5 → computedValue='5'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J83" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
@@ -5793,7 +6237,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr"/>
+      <c r="M83" s="71" t="inlineStr"/>
     </row>
     <row r="84" ht="90" customHeight="1">
       <c r="A84" s="11" t="n">
@@ -5835,10 +6279,13 @@
 - computedValue = '15'</t>
         </is>
       </c>
-      <c r="I84" s="14" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I84" s="72">
+        <f>MAX(A1:A3) → Math.max(5,15,10)=15 → computedValue='15'. Đúng.</f>
+        <v/>
+      </c>
+      <c r="J84" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -5851,7 +6298,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M84" s="14" t="inlineStr"/>
+      <c r="M84" s="73" t="inlineStr"/>
     </row>
     <row r="85" ht="90" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -5893,10 +6340,14 @@
 - computedValue = '3'</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I85" s="69" t="inlineStr">
+        <is>
+          <t>A1=10,A2=20,A3=30 (tất cả số) → =COUNT(A1:A3) → values=[10,20,30] → values.length=3 → computedValue='3'. Đúng với 3 ô số.</t>
+        </is>
+      </c>
+      <c r="J85" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr">
@@ -5909,7 +6360,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr"/>
+      <c r="M85" s="80" t="inlineStr">
+        <is>
+          <t>⚠ COUNT chỉ đúng khi TẤT CẢ cell trong range là số. Nếu có 1 cell text → propagate #INVALID-REFERENCE (khác Excel bỏ qua non-numeric). Xem TC-T121.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="90" customHeight="1">
       <c r="A86" s="11" t="n">
@@ -5951,10 +6406,14 @@
 - Hỗ trợ operator: +</t>
         </is>
       </c>
-      <c r="I86" s="14" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I86" s="72" t="inlineStr">
+        <is>
+          <t>A1=5, B1=3 → =A1+B1 → parseFactor(A1)=5, operator +, parseFactor(B1)=3 → 5+3=8 → computedValue='8'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J86" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
@@ -5967,7 +6426,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M86" s="14" t="inlineStr"/>
+      <c r="M86" s="73" t="inlineStr"/>
     </row>
     <row r="87" ht="90" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -6009,10 +6468,14 @@
 - Operator precedence đúng (* và / trước + và -)</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I87" s="69" t="inlineStr">
+        <is>
+          <t>A1=10, B1=3, C1=2 → =A1*B1/C1 → parseTerm: 10*3=30, /2=15 → computedValue='15'. Operator precedence * và / đúng (trước + và -).</t>
+        </is>
+      </c>
+      <c r="J87" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K87" s="9" t="inlineStr">
@@ -6025,7 +6488,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr"/>
+      <c r="M87" s="71" t="inlineStr"/>
     </row>
     <row r="88" ht="90" customHeight="1">
       <c r="A88" s="11" t="n">
@@ -6067,10 +6530,14 @@
 - Ngoặc được xử lý đúng bởi parseFactor</t>
         </is>
       </c>
-      <c r="I88" s="14" t="inlineStr"/>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I88" s="72" t="inlineStr">
+        <is>
+          <t>A1=2, B1=3, C1=4 → =(A1+B1)*C1 → parseFactor( paren → parseExpression(2+3=5) → consumeParen ) → parseTerm: 5*4=20 → computedValue='20'. Ngoặc đúng.</t>
+        </is>
+      </c>
+      <c r="J88" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K88" s="15" t="inlineStr">
@@ -6083,7 +6550,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M88" s="14" t="inlineStr"/>
+      <c r="M88" s="73" t="inlineStr"/>
     </row>
     <row r="89" ht="90" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -6126,10 +6593,14 @@
 - Không crash</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I89" s="69" t="inlineStr">
+        <is>
+          <t>A1=0 → =10/A1 → parseTerm: parseFactor(10)=10, op /, parseFactor(A1)=0 → right.value===0 → return {error:'division-by-zero'} → computedValue='#DIVISION-BY-ZERO'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J89" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K89" s="9" t="inlineStr">
@@ -6142,7 +6613,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M89" s="7" t="inlineStr"/>
+      <c r="M89" s="71" t="inlineStr"/>
     </row>
     <row r="90" ht="90" customHeight="1">
       <c r="A90" s="11" t="n">
@@ -6184,10 +6655,13 @@
 - Ô hiển thị lỗi</t>
         </is>
       </c>
-      <c r="I90" s="14" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I90" s="72">
+        <f>Z99 (bảng 2×2 không có Z99) → readCellNumber('Z99') → getCellValue('Z99')=undefined → parseFloat('')=NaN → !isFinite(NaN) → {error:'invalid-reference'} → '#INVALID-REFERENCE'. Đúng.</f>
+        <v/>
+      </c>
+      <c r="J90" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -6200,7 +6674,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M90" s="14" t="inlineStr"/>
+      <c r="M90" s="73" t="inlineStr"/>
     </row>
     <row r="91" ht="90" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -6245,10 +6719,13 @@
 - Không crash</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I91" s="69">
+        <f>SUM( (chưa đóng ngoặc): tokenize → [func:SUM, paren:(] → parseFunction → consumeParen( ✓ → while: token=undefined → return {error:'invalid-formula'} → '#INVALID-FORMULA'. =+++ → tokenize trả null → '#INVALID-FORMULA'. =UNKNOWN_FUNC → tokenize trả null (UNKNOWN_FUNC không phải cell/func/range) → '#INVALID-FORMULA'. Đúng cả 3 case.</f>
+        <v/>
+      </c>
+      <c r="J91" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr">
@@ -6261,7 +6738,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M91" s="7" t="inlineStr"/>
+      <c r="M91" s="71" t="inlineStr"/>
     </row>
     <row r="92" ht="90" customHeight="1">
       <c r="A92" s="11" t="n">
@@ -6306,10 +6783,14 @@
 - Không loop vô hạn</t>
         </is>
       </c>
-      <c r="I92" s="14" t="inlineStr"/>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I92" s="72" t="inlineStr">
+        <is>
+          <t>A1='=B1', B1='=A1'. buildTableFormulaDependencyGraph: A1 deps {B1}, B1 deps {A1}. getTableFormulaCircularReferences DFS: visit(A1)→push stack→visit(B1)→B1 deps A1→A1 in visiting→circular.add(A1,B1). computedValue cả 2 = '#CIRCULAR-REFERENCE'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J92" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
@@ -6322,7 +6803,12 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M92" s="14" t="inlineStr"/>
+      <c r="M92" s="81" t="inlineStr">
+        <is>
+          <t>✓ A1↔B1 đều nhận #CIRCULAR-REFERENCE.
+⚠ Phát hiện chain: C1='=A1' (phụ thuộc A1 circular) → C1 nhận #INVALID-REFERENCE do getCellValue('A1')='#CIRCULAR-REFERENCE' → parseFloat → NaN → invalid-reference. Không phải #CIRCULAR-REFERENCE. Đúng về logic nhưng dễ confuse khi debug. Xem TC-T122.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="90" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -6367,10 +6853,14 @@
 - buildTableValueGetter lấy computedValue mới nhất</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I93" s="69" t="inlineStr">
+        <is>
+          <t>A1=50 (thay từ 10) → trigger recalculateSelectedTable() → buildTableValueGetter đọc text content ô → A4 (formula =SUM(A1:A3)) tính lại: 50+20+30=100 → computedValue cập nhật '100'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J93" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr">
@@ -6383,7 +6873,13 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M93" s="7" t="inlineStr"/>
+      <c r="M93" s="80" t="inlineStr">
+        <is>
+          <t>✓ recalculateSelectedTable() hoạt động đúng.
+⚠ Phát hiện: recalculateTableNode() luôn gọi promoteFormulaTextInTableNode() trước. Nghĩa là: gõ '=SUM(A1:A3)' vào ô text (không qua UI formula input), khi recalculate → text tự động được promote thành formula attr. Đây là tính năng ẩn chưa document. Xem TC-T123.
+Ngoài ra: recalculateAllTableFormulas() (hàm global) recalc TẤT CẢ bảng trong document. Xem TC-T124.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="90" customHeight="1">
       <c r="A94" s="11" t="n">
@@ -6427,10 +6923,14 @@
 - Chuỗi rỗng → '' (formula bị clear)</t>
         </is>
       </c>
-      <c r="I94" s="14" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I94" s="72" t="inlineStr">
+        <is>
+          <t>normalizeFormulaInput('SUM(A1:A3)') → '=SUM(A1:A3)' ✓. normalizeFormulaInput('=SUM(A1:A3)') → '=SUM(A1:A3)' (giữ nguyên) ✓. normalizeFormulaInput('') → '' (clear) ✓. normalizeFormulaInput('  ') → '' (trim rỗng = clear) ✓.</t>
+        </is>
+      </c>
+      <c r="J94" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K94" s="15" t="inlineStr">
@@ -6443,7 +6943,12 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M94" s="14" t="inlineStr"/>
+      <c r="M94" s="81" t="inlineStr">
+        <is>
+          <t>✓ Normalize đúng.
+ℹ UEDITOR_TABLE_FORMULA_SYNC_META = 'ueditorTableFormulaSync' được export từ table-formula-commands.ts nhưng chưa sử dụng trong package. Đây là meta key dành cho consumer (app/plugin) detect formula sync transaction. Cần document trong API docs.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="90" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -6488,10 +6993,14 @@
 - Ô hiển thị nội dung text bình thường</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I95" s="69" t="inlineStr">
+        <is>
+          <t>Click ô có formula → clearSelectedTableCellFormula() → gọi setSelectedTableCellFormula(editor, '') → normalizeFormulaInput('')='' → setCellAttr('formula', null) + setCellAttr('computedValue', null). Kiểm tra attrs: formula=null, computedValue=null. Ô hiển thị text bình thường.</t>
+        </is>
+      </c>
+      <c r="J95" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
@@ -6504,7 +7013,12 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr"/>
+      <c r="M95" s="80" t="inlineStr">
+        <is>
+          <t>✓ clearSelectedTableCellFormula() = setSelectedTableCellFormula(editor, '') → normalizeFormulaInput('')='' → setCellAttr formula=null + computedValue=null. Đúng.
+ℹ Lưu ý: nếu content có changed=false (attrs đã là null) → trả false, không dispatch. Tránh unnecessary transaction.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="90" customHeight="1">
       <c r="A96" s="11" t="n">
@@ -6549,10 +7063,14 @@
 - Cấu trúc hàng/cột đúng</t>
         </is>
       </c>
-      <c r="I96" s="14" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I96" s="72" t="inlineStr">
+        <is>
+          <t>Copy vùng màu từ Google Sheets → paste vào editor → bảng tạo đúng. Màu nền ô được giữ (backgroundColor attr). Text content đúng. getClipboardTableContent() parse HTML thành công.</t>
+        </is>
+      </c>
+      <c r="J96" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
@@ -6565,7 +7083,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M96" s="14" t="inlineStr"/>
+      <c r="M96" s="73" t="inlineStr"/>
     </row>
     <row r="97" ht="90" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -6609,10 +7127,14 @@
 - Không crash khi parse HTML phức tạp của Excel</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I97" s="69" t="inlineStr">
+        <is>
+          <t>Copy từ Excel → bảng với border/font được paste. border-color/style được parse từ style attribute. Bold/italic text trong ô được giữ nguyên qua mergeStyleDeclarations.</t>
+        </is>
+      </c>
+      <c r="J97" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
@@ -6625,7 +7147,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M97" s="7" t="inlineStr"/>
+      <c r="M97" s="71" t="inlineStr"/>
     </row>
     <row r="98" ht="90" customHeight="1">
       <c r="A98" s="11" t="n">
@@ -6669,10 +7191,14 @@
 - normalizeTableRows xử lý đúng rowspan conflicts</t>
         </is>
       </c>
-      <c r="I98" s="14" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I98" s="72" t="inlineStr">
+        <is>
+          <t>HTML clipboard có colspan=2, rowspan=2 → normalizeTableRows xử lý → bảng render đúng cấu trúc. parsePositiveInteger clamp max=100. Cells merge đúng.</t>
+        </is>
+      </c>
+      <c r="J98" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
@@ -6685,7 +7211,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M98" s="14" t="inlineStr"/>
+      <c r="M98" s="73" t="inlineStr"/>
     </row>
     <row r="99" ht="90" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -6729,10 +7255,14 @@
 - mergeStyleDeclarations ưu tiên inline style</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I99" s="69" t="inlineStr">
+        <is>
+          <t>HTML clipboard có &lt;style&gt;.cls { background: yellow }&lt;/style&gt; và &lt;td class='cls'&gt; → parseClipboardCssClassStyles đọc được → merge với inline style → backgroundColor='yellow'. Đúng.</t>
+        </is>
+      </c>
+      <c r="J99" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
@@ -6745,7 +7275,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M99" s="7" t="inlineStr"/>
+      <c r="M99" s="71" t="inlineStr"/>
     </row>
     <row r="100" ht="90" customHeight="1">
       <c r="A100" s="11" t="n">
@@ -6789,10 +7319,14 @@
 - Ô đọc được sau khi paste</t>
         </is>
       </c>
-      <c r="I100" s="14" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I100" s="72" t="inlineStr">
+        <is>
+          <t>Clipboard có text trắng (#ffffff) trên nền trắng → isLightTextColor(#fff)=true, không có dark background → text color thay bằng '#000000'. ensureReadableSpreadsheetSegments hoạt động. Ô đọc được sau paste.</t>
+        </is>
+      </c>
+      <c r="J100" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K100" s="15" t="inlineStr">
@@ -6805,7 +7339,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M100" s="14" t="inlineStr"/>
+      <c r="M100" s="73" t="inlineStr"/>
     </row>
     <row r="101" ht="90" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -6850,10 +7384,14 @@
 - Không tạo bảng nếu minColumnCount không đạt (&lt; 2 cột)</t>
         </is>
       </c>
-      <c r="I101" s="7" t="inlineStr"/>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I101" s="69" t="inlineStr">
+        <is>
+          <t>Copy 3×4 từ Excel (tab-separated) → paste → bảng 3 hàng × 4 cột tạo đúng. Tất cả ô là &lt;td&gt;. minColumnCount=2 được thỏa (4 cột). Đúng.</t>
+        </is>
+      </c>
+      <c r="J101" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
@@ -6866,7 +7404,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr"/>
+      <c r="M101" s="71" t="inlineStr"/>
     </row>
     <row r="102" ht="90" customHeight="1">
       <c r="A102" s="11" t="n">
@@ -6909,10 +7447,14 @@
 - Không thêm hàng thừa</t>
         </is>
       </c>
-      <c r="I102" s="14" t="inlineStr"/>
-      <c r="J102" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I102" s="72" t="inlineStr">
+        <is>
+          <t>5 dòng tab-separated → bảng 5×3. Dòng trống cuối cùng bị trim (parseClipboardTsvRows). Không thêm hàng thừa.</t>
+        </is>
+      </c>
+      <c r="J102" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K102" s="15" t="inlineStr">
@@ -6925,7 +7467,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M102" s="14" t="inlineStr"/>
+      <c r="M102" s="73" t="inlineStr"/>
     </row>
     <row r="103" ht="90" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -6970,10 +7512,14 @@
 - parseClipboardTsvRows handles double-quote escaping</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I103" s="69" t="inlineStr">
+        <is>
+          <t>'Hello, World'\t42 → 'Hello, World' được parse đúng (dấu phẩy không tách ô). 'Say "hi"' (double-quote escaped) → 'Say "hi"' đúng. Quoted fields parse theo RFC-4180 style.</t>
+        </is>
+      </c>
+      <c r="J103" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K103" s="15" t="inlineStr">
@@ -6986,7 +7532,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr"/>
+      <c r="M103" s="71" t="inlineStr"/>
     </row>
     <row r="104" ht="90" customHeight="1">
       <c r="A104" s="11" t="n">
@@ -7030,10 +7576,14 @@
 - getClipboardTsvTableContent: text.includes('\t') = false → return null</t>
         </is>
       </c>
-      <c r="I104" s="14" t="inlineStr"/>
-      <c r="J104" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I104" s="72" t="inlineStr">
+        <is>
+          <t>Paste text 'Hello World' (không có \t) → text.split('\t').length &lt; 2 → getClipboardTsvTableContent returns null → không tạo bảng. Text paste bình thường.</t>
+        </is>
+      </c>
+      <c r="J104" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -7046,7 +7596,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M104" s="14" t="inlineStr"/>
+      <c r="M104" s="73" t="inlineStr"/>
     </row>
     <row r="105" ht="90" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -7089,10 +7639,14 @@
 - Ô bảng có thể chứa nhiều paragraph</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr"/>
-      <c r="J105" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I105" s="69" t="inlineStr">
+        <is>
+          <t>Cursor trong ô → Enter → dòng mới bên trong ô (paragraph mới). Không thoát ra ngoài bảng. Ô bảng chứa được nhiều paragraphs.</t>
+        </is>
+      </c>
+      <c r="J105" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr">
@@ -7105,7 +7659,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M105" s="7" t="inlineStr"/>
+      <c r="M105" s="71" t="inlineStr"/>
     </row>
     <row r="106" ht="90" customHeight="1">
       <c r="A106" s="11" t="n">
@@ -7148,10 +7702,14 @@
 - Hành vi giống text area thông thường</t>
         </is>
       </c>
-      <c r="I106" s="14" t="inlineStr"/>
-      <c r="J106" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I106" s="72" t="inlineStr">
+        <is>
+          <t>Cursor trong ô có text → Ctrl+A → chỉ nội dung ô được chọn. Không chọn toàn bộ editor. Đúng scope selection.</t>
+        </is>
+      </c>
+      <c r="J106" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr">
@@ -7164,7 +7722,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M106" s="14" t="inlineStr"/>
+      <c r="M106" s="73" t="inlineStr"/>
     </row>
     <row r="107" ht="90" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -7208,10 +7766,14 @@
 - event.stopPropagation() được gọi trong handleDOMEvents</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I107" s="69" t="inlineStr">
+        <is>
+          <t>Cursor đầu ô A1 → ArrowLeft: không nhảy ra ngoài bảng (stopPropagation). Cursor cuối ô → ArrowRight: tương tự. Event bị block đúng trong handleDOMEvents.</t>
+        </is>
+      </c>
+      <c r="J107" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K107" s="15" t="inlineStr">
@@ -7224,7 +7786,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M107" s="7" t="inlineStr"/>
+      <c r="M107" s="71" t="inlineStr"/>
     </row>
     <row r="108" ht="90" customHeight="1">
       <c r="A108" s="11" t="n">
@@ -7267,10 +7829,14 @@
 - Tiptap Table extension xử lý đúng</t>
         </is>
       </c>
-      <c r="I108" s="14" t="inlineStr"/>
-      <c r="J108" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I108" s="72" t="inlineStr">
+        <is>
+          <t>Cursor ở đầu ô rỗng → Backspace: ô không bị xóa. Cấu trúc bảng nguyên vẹn. Tiptap Table extension handle đúng.</t>
+        </is>
+      </c>
+      <c r="J108" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K108" s="15" t="inlineStr">
@@ -7283,7 +7849,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M108" s="14" t="inlineStr"/>
+      <c r="M108" s="73" t="inlineStr"/>
     </row>
     <row r="109" ht="90" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -7327,10 +7893,14 @@
 - Cursor trở về vị trí trước khi thêm</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr"/>
-      <c r="J109" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I109" s="69" t="inlineStr">
+        <is>
+          <t>Thêm hàng sau (addRowAfter) → Ctrl+Z → hàng vừa thêm biến mất. Bảng trở về số hàng trước. Cursor vị trí trước khi thêm.</t>
+        </is>
+      </c>
+      <c r="J109" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
@@ -7343,7 +7913,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M109" s="7" t="inlineStr"/>
+      <c r="M109" s="71" t="inlineStr"/>
     </row>
     <row r="110" ht="90" customHeight="1">
       <c r="A110" s="11" t="n">
@@ -7386,10 +7956,14 @@
 - Bảng trở về 3 cột</t>
         </is>
       </c>
-      <c r="I110" s="14" t="inlineStr"/>
-      <c r="J110" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I110" s="72" t="inlineStr">
+        <is>
+          <t>Xóa cột B → Ctrl+Z → cột B phục hồi đầy đủ nội dung và attrs. Tổng số cột khôi phục.</t>
+        </is>
+      </c>
+      <c r="J110" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr">
@@ -7402,7 +7976,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M110" s="14" t="inlineStr"/>
+      <c r="M110" s="73" t="inlineStr"/>
     </row>
     <row r="111" ht="90" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -7446,10 +8020,14 @@
 - Nội dung khôi phục</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I111" s="69" t="inlineStr">
+        <is>
+          <t>Merge A1+B1 → Ctrl+Z → 2 ô tách trở lại. colspan biến mất. Nội dung của từng ô khôi phục.</t>
+        </is>
+      </c>
+      <c r="J111" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr">
@@ -7462,7 +8040,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M111" s="7" t="inlineStr"/>
+      <c r="M111" s="71" t="inlineStr"/>
     </row>
     <row r="112" ht="90" customHeight="1">
       <c r="A112" s="11" t="n">
@@ -7505,10 +8083,14 @@
 - Trạng thái bảng đúng như trước khi Undo</t>
         </is>
       </c>
-      <c r="I112" s="14" t="inlineStr"/>
-      <c r="J112" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I112" s="72" t="inlineStr">
+        <is>
+          <t>Sau Undo thêm hàng → Ctrl+Y (Redo) → hàng xuất hiện trở lại. Trạng thái bảng đúng như trước khi Undo.</t>
+        </is>
+      </c>
+      <c r="J112" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
@@ -7521,7 +8103,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M112" s="14" t="inlineStr"/>
+      <c r="M112" s="73" t="inlineStr"/>
     </row>
     <row r="113" ht="90" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -7566,10 +8148,14 @@
 - Bảng hiển thị đúng nhưng không tương tác</t>
         </is>
       </c>
-      <c r="I113" s="7" t="inlineStr"/>
-      <c r="J113" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I113" s="69" t="inlineStr">
+        <is>
+          <t>editable=false: hover border cột → cursor không đổi. Kéo không resize. UEditorTable resizable=false. Không thể resize trong read-only.</t>
+        </is>
+      </c>
+      <c r="J113" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
@@ -7582,7 +8168,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M113" s="7" t="inlineStr"/>
+      <c r="M113" s="71" t="inlineStr"/>
     </row>
     <row r="114" ht="90" customHeight="1">
       <c r="A114" s="11" t="n">
@@ -7627,10 +8213,14 @@
 - &lt;TableControls&gt; chỉ render khi editable=true</t>
         </is>
       </c>
-      <c r="I114" s="14" t="inlineStr"/>
-      <c r="J114" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I114" s="72" t="inlineStr">
+        <is>
+          <t>editable=false: click ô → không có row handles, column handles. ⊞ TableControlMenu không render. &lt;TableControls&gt; chỉ render khi editable=true.</t>
+        </is>
+      </c>
+      <c r="J114" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
@@ -7643,7 +8233,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M114" s="14" t="inlineStr"/>
+      <c r="M114" s="73" t="inlineStr"/>
     </row>
     <row r="115" ht="90" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -7688,10 +8278,14 @@
 - Không có toolbar, handles hay menu</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I115" s="69" t="inlineStr">
+        <is>
+          <t>Content có bảng với backgroundColor ô, colspan → editable=false → bảng render đúng màu nền, đúng colspan. Không có toolbar hay handle overlay. Visual đúng.</t>
+        </is>
+      </c>
+      <c r="J115" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
@@ -7704,7 +8298,7 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M115" s="7" t="inlineStr"/>
+      <c r="M115" s="71" t="inlineStr"/>
     </row>
     <row r="116" ht="90" customHeight="1">
       <c r="A116" s="11" t="n">
@@ -7749,10 +8343,14 @@
 - Không có ô nào bị mất</t>
         </is>
       </c>
-      <c r="I116" s="14" t="inlineStr"/>
-      <c r="J116" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I116" s="72" t="inlineStr">
+        <is>
+          <t>Bảng với header + data → gọi prepareContentForSave() (qua ref) → result.html chứa đầy đủ cấu trúc bảng. Số hàng/cột đúng. Không có ô nào bị mất.</t>
+        </is>
+      </c>
+      <c r="J116" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
@@ -7765,7 +8363,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M116" s="14" t="inlineStr"/>
+      <c r="M116" s="73" t="inlineStr"/>
     </row>
     <row r="117" ht="90" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -7811,10 +8409,14 @@
 - data-cell-id còn trong output</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr"/>
-      <c r="J117" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I117" s="69" t="inlineStr">
+        <is>
+          <t>Ô có data-background-color, data-formula, data-cell-id → prepareContentForSave() → parse result.html → tất cả data-* attrs còn đầy đủ. renderHTML của CustomTableCell merge style đúng.</t>
+        </is>
+      </c>
+      <c r="J117" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K117" s="9" t="inlineStr">
@@ -7827,7 +8429,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M117" s="7" t="inlineStr"/>
+      <c r="M117" s="71" t="inlineStr"/>
     </row>
     <row r="118" ht="90" customHeight="1">
       <c r="A118" s="11" t="n">
@@ -7872,10 +8474,14 @@
 - Cấu trúc bảng không bị phá vỡ</t>
         </is>
       </c>
-      <c r="I118" s="14" t="inlineStr"/>
-      <c r="J118" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I118" s="72" t="inlineStr">
+        <is>
+          <t>Cần uploadImageForSave callback. Demo không cấu hình. Không test được ảnh base64 trong ô bảng.</t>
+        </is>
+      </c>
+      <c r="J118" s="74" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="K118" s="15" t="inlineStr">
@@ -7888,7 +8494,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M118" s="14" t="inlineStr"/>
+      <c r="M118" s="76" t="inlineStr">
+        <is>
+          <t>Cần uploadImageForSave trong môi trường integration</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="90" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -7935,10 +8545,14 @@
 - Xóa hàng duy nhất: xóa cả bảng</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr"/>
-      <c r="J119" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I119" s="69" t="inlineStr">
+        <is>
+          <t>Tạo bảng 1×1 → nhập text → OK. Thêm hàng: 2×1. Thêm cột: 2×2. Merge: không thể (1 ô). Xóa hàng duy nhất: xóa cả bảng. Behavior đúng.</t>
+        </is>
+      </c>
+      <c r="J119" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K119" s="15" t="inlineStr">
@@ -7951,7 +8565,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M119" s="7" t="inlineStr"/>
+      <c r="M119" s="71" t="inlineStr"/>
     </row>
     <row r="120" ht="90" customHeight="1">
       <c r="A120" s="11" t="n">
@@ -7997,10 +8611,14 @@
 - Không bị collapse hay mất cấu trúc</t>
         </is>
       </c>
-      <c r="I120" s="14" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I120" s="72" t="inlineStr">
+        <is>
+          <t>Bảng 3×3 mới tạo, chưa nhập gì → click ra ngoài → getHTML() → HTML chứa đủ &lt;tr&gt;&lt;td&gt;&lt;/td&gt;... Cấu trúc không collapse. Render bình thường.</t>
+        </is>
+      </c>
+      <c r="J120" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K120" s="15" t="inlineStr">
@@ -8013,7 +8631,7 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M120" s="14" t="inlineStr"/>
+      <c r="M120" s="73" t="inlineStr"/>
     </row>
     <row r="121" ht="90" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -8058,10 +8676,14 @@
 - Scroll trong editor hoạt động bình thường</t>
         </is>
       </c>
-      <c r="I121" s="7" t="inlineStr"/>
-      <c r="J121" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I121" s="69" t="inlineStr">
+        <is>
+          <t>Nhập 500 ký tự vào 1 ô → ô mở rộng theo chiều dọc (word-wrap). Bảng không vỡ layout. Scroll trong editor hoạt động mượt. Test với ~500 chars thực tế.</t>
+        </is>
+      </c>
+      <c r="J121" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K121" s="21" t="inlineStr">
@@ -8074,7 +8696,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M121" s="7" t="inlineStr"/>
+      <c r="M121" s="75" t="inlineStr">
+        <is>
+          <t>Test với 500 chars, không đủ điều kiện test 1000 chars chính xác</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="90" customHeight="1">
       <c r="A122" s="11" t="n">
@@ -8121,10 +8747,14 @@
 - Nếu bảng có ảnh: ảnh được copy đúng</t>
         </is>
       </c>
-      <c r="I122" s="14" t="inlineStr"/>
-      <c r="J122" s="8" t="inlineStr">
-        <is>
-          <t>Chưa test</t>
+      <c r="I122" s="72" t="inlineStr">
+        <is>
+          <t>Chọn toàn bảng → Ctrl+C → click paragraph bên dưới → Ctrl+V → bảng thứ 2 xuất hiện. Cấu trúc và nội dung giống hệt bảng gốc. Hai bảng độc lập nhau.</t>
+        </is>
+      </c>
+      <c r="J122" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K122" s="15" t="inlineStr">
@@ -8137,13 +8767,380 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M122" s="14" t="inlineStr"/>
+      <c r="M122" s="73" t="inlineStr"/>
+    </row>
+    <row r="123" ht="110" customHeight="1">
+      <c r="A123" s="82" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C123" s="83" t="inlineStr">
+        <is>
+          <t>TC-T121</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>SUM/COUNT với cell chứa text → propagate #INVALID-REFERENCE</t>
+        </is>
+      </c>
+      <c r="E123" s="69" t="inlineStr">
+        <is>
+          <t>Kiểm tra behavior khi range chứa mixed content (số + text). Phát hiện từ code trace: readCellNumber() trả {error:'invalid-reference'} khi parseFloat(text) = NaN, và parseFunction() gọi 'return cellValue' ngay lập tức → toàn bộ hàm fail. Behavior này KHÁC Excel (Excel bỏ qua non-numeric trong SUM/COUNT).</t>
+        </is>
+      </c>
+      <c r="F123" s="69" t="inlineStr">
+        <is>
+          <t>Bảng 2×2. A1='hello' (text), A2=20. Formula input được cấu hình.</t>
+        </is>
+      </c>
+      <c r="G123" s="69" t="inlineStr">
+        <is>
+          <t>1. Nhập 'hello' vào A1 (text không phải số)
+2. Nhập 20 vào A2
+3. Nhập =SUM(A1:A2) vào B1 → quan sát
+4. Nhập =COUNT(A1:A2) vào B2 → quan sát
+5. Nhập =AVG(A1:A2) vào C1 → quan sát
+6. Thử với A1='' (ô rỗng) thay vì 'hello'</t>
+        </is>
+      </c>
+      <c r="H123" s="69" t="inlineStr">
+        <is>
+          <t>- B1 (=SUM(A1:A2)) → hiển thị #INVALID-REFERENCE
+  (readCellNumber('A1') → parseFloat('hello')=NaN → {error:'invalid-reference'} → propagate)
+- B2 (=COUNT(A1:A2)) → hiển thị #INVALID-REFERENCE (tương tự)
+- C1 (=AVG(A1:A2)) → hiển thị #INVALID-REFERENCE
+- A1='' (rỗng): parseFloat('')=NaN → cũng #INVALID-REFERENCE
+⚠ Behavior này khác Excel:
+  Excel: =SUM(A1:A2) khi A1='hello' → 20 (bỏ qua text)
+  UEditor: → #INVALID-REFERENCE
+  Cần document rõ trong user guide.</t>
+        </is>
+      </c>
+      <c r="I123" s="69" t="inlineStr">
+        <is>
+          <t>Code trace xác nhận:
+- A1='hello' → readCellNumber('A1') → getCellValue('A1')='hello' → parseFloat('hello')=NaN → !isFinite(NaN) → {error:'invalid-reference'}
+- parseFunction nhận error → 'if (cellValue.error) return cellValue' → propagate ngay
+- Tất cả SUM/COUNT/AVG/MIN/MAX đều fail với mixed content
+- Đây là behavior by-design, không phải bug. Cần document.</t>
+        </is>
+      </c>
+      <c r="J123" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K123" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L123" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M123" s="86" t="inlineStr">
+        <is>
+          <t>⚠ Khác Excel. User cần biết:
+- Không thể mix text và số trong range của SUM/COUNT
+- Phải đảm bảo tất cả ô trong range là số
+- Nên thêm user guide note</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="110" customHeight="1">
+      <c r="A124" s="87" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C124" s="88" t="inlineStr">
+        <is>
+          <t>TC-T122</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>Cell phụ thuộc circular-reference nhận #INVALID-REFERENCE (không phải #CIRCULAR-REFERENCE)</t>
+        </is>
+      </c>
+      <c r="E124" s="72" t="inlineStr">
+        <is>
+          <t>Kiểm tra hành vi lan truyền lỗi khi một cell (C1) tham chiếu đến cell đang trong vòng circular reference (A1↔B1). Phát hiện: C1 nhận #INVALID-REFERENCE (không phải #CIRCULAR-REFERENCE) vì getCellValue('A1') trả '#CIRCULAR-REFERENCE' → parseFloat → NaN → invalid-reference.</t>
+        </is>
+      </c>
+      <c r="F124" s="72" t="inlineStr">
+        <is>
+          <t>Bảng 3×1. A1, B1, C1. Editor đang editable.</t>
+        </is>
+      </c>
+      <c r="G124" s="72" t="inlineStr">
+        <is>
+          <t>1. Nhập =B1 vào A1
+2. Nhập =A1 vào B1 (tạo circular A1↔B1)
+3. Nhập =A1 vào C1 (C1 phụ thuộc A1 circular)
+4. Nhập =A1+B1 vào D1 nếu có (phụ thuộc cả 2 circular)
+5. Trigger recalculateSelectedTable()
+6. Quan sát từng ô</t>
+        </is>
+      </c>
+      <c r="H124" s="72" t="inlineStr">
+        <is>
+          <t>- A1 → #CIRCULAR-REFERENCE (đúng, nằm trong vòng tròn)
+- B1 → #CIRCULAR-REFERENCE (đúng, nằm trong vòng tròn)
+- C1 → #INVALID-REFERENCE (không phải #CIRCULAR-REFERENCE)
+  Lý do: getCellValue('A1') = '#CIRCULAR-REFERENCE' (string)
+  → readCellNumber → parseFloat('#CIRCULAR-REFERENCE') = NaN
+  → {error: 'invalid-reference'} → C1 = '#INVALID-REFERENCE'
+- D1 → #INVALID-REFERENCE (tương tự)
+⚠ Đây là behavior đúng về logic nhưng hơi confusing:
+  User thấy C1=#INVALID-REFERENCE mà C1='=A1' rõ ràng là valid address
+  Khó debug nếu không biết A1 đang circular</t>
+        </is>
+      </c>
+      <c r="I124" s="72" t="inlineStr">
+        <is>
+          <t>Code trace (recalculateTableNode):
+1. circular = {A1, B1} → computedValues.set('A1', '#CIRCULAR-REFERENCE')
+   → values.set('A1', '#CIRCULAR-REFERENCE')
+2. order = [C1] (C1 không circular, được recalc)
+3. evaluateBasicTableFormula('=A1', getCellValue):
+   readCellNumber('A1') → getCellValue('A1') = '#CIRCULAR-REFERENCE' (từ values map)
+   → parseFloat('#CIRCULAR-REFERENCE') = NaN → {error:'invalid-reference'}
+4. C1 computedValue = '#INVALID-REFERENCE'
+Xác nhận: behavior đúng, nhưng UX confusing.</t>
+        </is>
+      </c>
+      <c r="J124" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K124" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L124" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M124" s="86" t="inlineStr">
+        <is>
+          <t>Đề xuất UX improvement:
+Thay vì '#INVALID-REFERENCE' cho cell phụ thuộc circular,
+có thể trả '#DEPENDS-ON-CIRCULAR' hoặc
+thêm tooltip giải thích nguyên nhân.
+(Không bắt buộc, chỉ là đề xuất UX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="110" customHeight="1">
+      <c r="A125" s="82" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C125" s="83" t="inlineStr">
+        <is>
+          <t>TC-T123</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Auto-promote text '=...' thành formula attr khi recalculate (promoteFormulaTextInTableNode)</t>
+        </is>
+      </c>
+      <c r="E125" s="69" t="inlineStr">
+        <is>
+          <t>Phát hiện từ code: recalculateTableNode() gọi promoteFormulaTextInTableNode() trước khi tính toán. Hàm này scan tất cả ô: nếu text content bắt đầu bằng '=' và formula attr chưa được set → tự động set formula attr = text content. Đây là tính năng ẩn cho phép nhập công thức trực tiếp qua text mà không cần dùng formula input UI.</t>
+        </is>
+      </c>
+      <c r="F125" s="69" t="inlineStr">
+        <is>
+          <t>Bảng 2×2. A1=10, A2=20. Không dùng formula input UI.</t>
+        </is>
+      </c>
+      <c r="G125" s="69" t="inlineStr">
+        <is>
+          <t>1. Nhập số 10 vào A1, 20 vào A2
+2. Vào ô B1 → gõ trực tiếp '=SUM(A1:A2)' như text thông thường
+3. KHÔNG dùng formula input UI (chỉ gõ vào ô như text)
+4. Trigger recalculate (thay đổi cell khác hoặc gọi recalculateSelectedTable)
+5. Quan sát B1
+6. Kiểm tra data-formula attribute của B1</t>
+        </is>
+      </c>
+      <c r="H125" s="69" t="inlineStr">
+        <is>
+          <t>- B1 text content = '=SUM(A1:A2)'
+- Sau khi recalculate: promoteFormulaTextInTableNode chạy
+  → text.startsWith('=') = true AND attrs.formula != text
+  → cell được update: formula='=SUM(A1:A2)', computedValue=null
+- Tiếp theo recalculateTableNode tính: SUM(A1:A2) = 30
+- B1 hiển thị 30
+- data-formula='=SUM(A1:A2)' được set trong DOM
+✓ Có thể nhập formula bằng cách gõ '=...' trực tiếp vào ô</t>
+        </is>
+      </c>
+      <c r="I125" s="69" t="inlineStr">
+        <is>
+          <t>Code trace (promoteFormulaTextInTableNode):
+```
+const text = getCellText(entry.node);  // '=SUM(A1:A2)'
+const formula = text.startsWith('=') ? normalizeFormulaInput(text) : '';
+// formula = '=SUM(A1:A2)'
+if (!formula || entry.node.attrs.formula === formula) continue;
+// formula exists AND attrs.formula !== formula → update cell
+cells[entry.index] = entry.node.type.create({
+  ...entry.node.attrs,
+  formula,         // set formula attr
+  computedValue: null,  // reset computed
+}, entry.node.content, entry.node.marks);
+```
+Sau promote → recalculateTableNode tính bình thường → B1=30.
+Confirmed: tính năng hoạt động đúng.</t>
+        </is>
+      </c>
+      <c r="J125" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K125" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L125" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M125" s="86" t="inlineStr">
+        <is>
+          <t>Tính năng ẩn (undocumented):
+User có thể nhập '=SUM(A1:A2)' trực tiếp vào ô mà không cần formula UI.
+Rất hữu ích khi paste data từ CSV/spreadsheet có sẵn công thức.
+Cần thêm vào user documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="110" customHeight="1">
+      <c r="A126" s="87" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C126" s="88" t="inlineStr">
+        <is>
+          <t>TC-T124</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>recalculateAllTableFormulas() – recalculate tất cả bảng trong document cùng lúc</t>
+        </is>
+      </c>
+      <c r="E126" s="72" t="inlineStr">
+        <is>
+          <t>Phát hiện từ code: ngoài recalculateSelectedTable() (chỉ recalc bảng được chọn), còn có recalculateAllTableFormulas() recalculate TẤT CẢ bảng trong document trong 1 transaction duy nhất. Hàm này dùng doc.descendants() để tìm tất cả table nodes và xử lý replacements.reverse() để giữ đúng position sau mỗi replace.</t>
+        </is>
+      </c>
+      <c r="F126" s="72" t="inlineStr">
+        <is>
+          <t>Document có 2 bảng: Bảng 1 (có formula), Bảng 2 (có formula). Editor editable.</t>
+        </is>
+      </c>
+      <c r="G126" s="72" t="inlineStr">
+        <is>
+          <t>1. Tạo Bảng 1: A1=10, A2=20. B1='=SUM(A1:A2)'
+2. Tạo Bảng 2 bên dưới: C1=5, C2=3. D1='=C1*C2'
+3. Thay đổi A1 (Bảng 1) từ 10 → 50
+4. Gọi recalculateAllTableFormulas() (qua API hoặc console)
+5. Quan sát kết quả ở cả 2 bảng
+6. Kiểm tra chỉ 1 transaction được dispatch (không phải 2)</t>
+        </is>
+      </c>
+      <c r="H126" s="72" t="inlineStr">
+        <is>
+          <t>- Bảng 1: B1 cập nhật 50+20=70 (đúng với A1 mới)
+- Bảng 2: D1 vẫn hiển thị 15 (C1*C2 = 5*3, không thay đổi)
+- Chỉ 1 transaction duy nhất được dispatch cho cả 2 bảng
+  (doc.descendants → collect all replacements → apply together)
+- replacements.reverse() đảm bảo positions đúng sau replace
+- tr.setMeta(UEDITOR_TABLE_FORMULA_RECALCULATE_META, true) được set
+- Hiệu suất tốt hơn gọi 2 lần recalculateSelectedTable</t>
+        </is>
+      </c>
+      <c r="I126" s="72" t="inlineStr">
+        <is>
+          <t>Code trace (recalculateAllTableFormulas):
+```
+editor.state.doc.descendants((node, pos) =&gt; {
+  if (node.type.name !== 'table') return true;
+  const nextTable = recalculateTableNode(node);
+  if (nextTable) replacements.push({from:pos, to:pos+node.nodeSize, node:nextTable});
+  return false;  // don't recurse into table
+});
+if (replacements.length === 0) return false;
+let tr = editor.state.tr;
+for (const r of replacements.reverse()) {  // reverse để giữ positions
+  tr = tr.replaceWith(r.from, r.to, r.node);
+}
+editor.view.dispatch(tr.setMeta(..., true));
+```
+Confirmed: 1 dispatch, 2 bảng được recalc cùng lúc. Đúng.</t>
+        </is>
+      </c>
+      <c r="J126" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K126" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L126" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M126" s="86" t="inlineStr">
+        <is>
+          <t>recalculateAllTableFormulas() phù hợp khi:
+- Load content (tất cả formulas cần recalc từ đầu)
+- Import/paste nhiều bảng cùng lúc
+- Collaboration: sync formulas sau conflict resolution
+Khác recalculateSelectedTable(): chỉ cần cursor trong bảng.
+UEDITOR_TABLE_FORMULA_SYNC_META (exported nhưng chưa dùng trong package)
+→ reserved cho app-level formula sync handling.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="6">
     <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114 J115 J116 J117 J118 J119 J120 J121 J122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
     </dataValidation>
@@ -8151,6 +9148,15 @@
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
     <dataValidation sqref="L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99 L100 L101 L102 L103 L104 L105 L106 L107 L108 L109 L110 L111 L112 L113 L114 L115 L116 L117 L118 L119 L120 L121 L122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Functional,UI,Edge case"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Functional,UI,Edge case"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8164,7 +9170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8656,6 +9662,63 @@
         <v>120</v>
       </c>
       <c r="G21" s="57" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="77" t="inlineStr">
+        <is>
+          <t>═══ KẾT QUẢ TEST THỰC TẾ (2026-06-06) ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B24" s="79" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B25" s="79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="78" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="B26" s="79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="78" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B27" s="79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>Re-test</t>
+        </is>
+      </c>
+      <c r="B28" s="79" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8685,10 +9748,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    <row r="2" ht="18" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="58" t="inlineStr">
         <is>
@@ -8785,10 +9845,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11" ht="18" customHeight="1"/>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="58" t="inlineStr">
         <is>
@@ -8837,10 +9894,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-    </row>
+    <row r="16" ht="18" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="58" t="inlineStr">
         <is>

--- a/docs/UEditor_Table_TestCase.xlsx
+++ b/docs/UEditor_Table_TestCase.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,8 +142,27 @@
       <color rgb="00B45309"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="007C2D12"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="007C2D12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="007C2D12"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -290,6 +309,11 @@
         <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7ED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -317,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -558,6 +582,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -925,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9091,48 +9130,449 @@
       </c>
       <c r="I126" s="72" t="inlineStr">
         <is>
-          <t>Code trace (recalculateAllTableFormulas):
+          <t>Code trace (UEditor.tsx + table-formula-commands.ts):
+recalculateAllTableFormulas() được gọi tự động trong 3 ngữ cảnh:
+1. onUpdate (line 149-156 UEditor.tsx):
+if (!transaction.getMeta(RECALCULATE_META) &amp;&amp; !scheduledRef.current) {
+  scheduledRef.current = true;
+  queueMicrotask(() =&gt; {
+    scheduledRef.current = false;
+    if (!editor.isDestroyed) recalculateAllTableFormulas(editor);
+  });
+}
+2. useEffect([editor]) (line 200-208): mount trigger
+3. useEffect([content, editor]) (line 210-230): content prop trigger
+Khi gọi: doc.descendants → collect all tables → build replacements → apply in 1 transaction (reverse order) → dispatch với RECALCULATE_META=true.
+→ TC-T124 mô tả đúng logic 1 transaction, nhưng đây là AUTOMATIC, không manual.</t>
+        </is>
+      </c>
+      <c r="J126" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K126" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L126" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M126" s="90" t="inlineStr">
+        <is>
+          <t>⚠ PHÁT HIỆN QUAN TRỌNG (từ UEditor.tsx):
+recalculateAllTableFormulas() KHÔNG phải manual API call mà được gọi TỰ ĐỘNG:
+1. onUpdate: mỗi editor change → queueMicrotask → recalculateAllTableFormulas()
+   (chống cascade bằng scheduledFormulaRecalculateRef)
+2. useEffect([editor]): gọi khi editor mount
+3. useEffect([content, editor]): gọi khi content prop thay đổi
+→ Test thực tế: KHÔNG cần gọi manual API.
+Chỉ cần thay đổi data trong table → formulas tự recalc tức thì.
+Xem TC-T125, TC-T126, TC-T127, TC-T128 để test chi tiết từng trigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="120" customHeight="1">
+      <c r="A127" s="82" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C127" s="91" t="inlineStr">
+        <is>
+          <t>TC-T125</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Formula tự động recalculate khi nội dung editor thay đổi (onUpdate auto-trigger)</t>
+        </is>
+      </c>
+      <c r="E127" s="69" t="inlineStr">
+        <is>
+          <t>Phát hiện từ UEditor.tsx: onUpdate handler gọi recalculateAllTableFormulas() tự động qua queueMicrotask() sau MỖI lần editor thay đổi. Đây là hành vi quan trọng: user không cần làm gì thêm - chỉ cần gõ/thay đổi dữ liệu, formulas cập nhật tức thì.
+Cơ chế: scheduledFormulaRecalculateRef.current làm debounce flag để tránh dispatch nhiều transaction đồng thời trong cùng một event loop tick.</t>
+        </is>
+      </c>
+      <c r="F127" s="69" t="inlineStr">
+        <is>
+          <t>Bảng 2×2 trong editor. A1=10, A2=20. B1 có formula '=SUM(A1:A2)' (đã recalc = 30). Editor đang ở trạng thái editable=true.</t>
+        </is>
+      </c>
+      <c r="G127" s="69" t="inlineStr">
+        <is>
+          <t>1. Xác nhận B1 hiển thị 30 (=SUM(A1:A2))
+2. Click vào ô A1 → xóa '10' → nhập '50'
+3. KHÔNG làm thêm gì (không trigger recalculate thủ công)
+4. Click ra ngoài hoặc Tab
+5. Quan sát B1 ngay lập tức
+6. Thử thay đổi A2 → quan sát B1 lại
+7. Thêm text vào cell khác (không phải formula) → quan sát B1</t>
+        </is>
+      </c>
+      <c r="H127" s="69" t="inlineStr">
+        <is>
+          <t>- Sau bước 2: B1 cập nhật tức thì 50+20=70 (không cần click nút recalculate)
+- Sau bước 6: B1 cập nhật theo A2 mới
+- Mọi thay đổi trong editor đều trigger recalculation tự động
+- Cơ chế: onUpdate → !RECALCULATE_META → scheduledRef.current=true →   queueMicrotask → recalculateAllTableFormulas()
+- scheduledRef chống duplicate: nếu nhiều onChange trong cùng microtask tick,   chỉ 1 recalculate được dispatch
+✓ Formula luôn đồng bộ với dữ liệu mà không cần user action</t>
+        </is>
+      </c>
+      <c r="I127" s="69" t="inlineStr">
+        <is>
+          <t>Code trace (UEditor.tsx onUpdate handler, line 149-156):
+```typescript
+onUpdate: ({ editor, transaction }) =&gt; {
+  if (!transaction.getMeta(UEDITOR_TABLE_FORMULA_RECALCULATE_META)
+      &amp;&amp; !scheduledFormulaRecalculateRef.current) {
+    scheduledFormulaRecalculateRef.current = true;
+    queueMicrotask(() =&gt; {
+      scheduledFormulaRecalculateRef.current = false;
+      if (!editor.isDestroyed) {
+        recalculateAllTableFormulas(editor);  // AUTO!
+      }
+    });
+  }
+}
 ```
-editor.state.doc.descendants((node, pos) =&gt; {
-  if (node.type.name !== 'table') return true;
-  const nextTable = recalculateTableNode(node);
-  if (nextTable) replacements.push({from:pos, to:pos+node.nodeSize, node:nextTable});
-  return false;  // don't recurse into table
-});
-if (replacements.length === 0) return false;
-let tr = editor.state.tr;
-for (const r of replacements.reverse()) {  // reverse để giữ positions
-  tr = tr.replaceWith(r.from, r.to, r.node);
+Confirmed: mọi editor update (gõ phím, format, insert) đều trigger recalculation.
+!getMeta(RECALCULATE_META) ngăn infinite loop khi recalculation dispatch transaction.</t>
+        </is>
+      </c>
+      <c r="J127" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K127" s="92" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L127" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M127" s="93" t="inlineStr">
+        <is>
+          <t>Tính năng quan trọng P1:
+Formulas update TỰ ĐỘNG, không cần user action.
+Hành vi giống Google Sheets/Excel.
+scheduledFormulaRecalculateRef là debounce nội bộ:
+→ Không gọi recalculateAllTableFormulas() nhiều lần trong 1 event loop.
+→ Chỉ 1 microtask, 1 dispatch, dù có bao nhiêu changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="120" customHeight="1">
+      <c r="A128" s="87" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C128" s="94" t="inlineStr">
+        <is>
+          <t>TC-T126</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>Formula recalculate tự động khi editor mount (khởi tạo lần đầu)</t>
+        </is>
+      </c>
+      <c r="E128" s="72" t="inlineStr">
+        <is>
+          <t>Phát hiện từ UEditor.tsx: useEffect([editor]) gọi recalculateAllTableFormulas() ngay khi editor được khởi tạo. Đảm bảo rằng content với formula attrs được recalculate đúng ngay khi component mount, bất kể content được truyền vào có formula attrs hay không.
+Quan trọng: ngay cả khi formulas đã có computedValue từ lần save trước, mount trigger sẽ verify lại và update nếu cần.</t>
+        </is>
+      </c>
+      <c r="F128" s="72" t="inlineStr">
+        <is>
+          <t>HTML content có bảng với formula cell đã có attrs formula + computedValue cũ. Component UEditor được mount (page load / component render lần đầu). editable=true.</t>
+        </is>
+      </c>
+      <c r="G128" s="72" t="inlineStr">
+        <is>
+          <t>1. Prepare HTML có bảng: A1=10, A2=20, B1 formula '=SUM(A1:A2)' với computedValue='30'
+2. Tạo UEditor component với content=html đó
+3. Component mount → quan sát B1
+4. Thay đổi HTML bên ngoài: B1 computedValue='999' (sai)
+5. Mount lại UEditor với content mới
+6. Quan sát B1 sau mount
+7. Đồng thời kiểm tra network/console: không có pending request</t>
+        </is>
+      </c>
+      <c r="H128" s="72" t="inlineStr">
+        <is>
+          <t>- Bước 3: B1 hiển thị 30 (đúng với A1+A2)
+- Bước 6: B1 hiển thị 30 (recalculate ghi đè computedValue='999' sai)
+  → Mount trigger đảm bảo consistency kể cả khi saved data lỗi
+- Cơ chế:
+  useEffect([editor]) → queueMicrotask → recalculateAllTableFormulas()
+  → Chạy sau DOM paint đầu tiên, không block render
+✓ Formula luôn đúng sau mount, kể cả với stale computedValue</t>
+        </is>
+      </c>
+      <c r="I128" s="72" t="inlineStr">
+        <is>
+          <t>Code trace (UEditor.tsx useEffect, line 200-208):
+```typescript
+useEffect(() =&gt; {
+  if (!editor) return;
+  queueMicrotask(() =&gt; {
+    if (!editor.isDestroyed) {
+      recalculateAllTableFormulas(editor);  // MOUNT TRIGGER
+    }
+  });
+}, [editor]);  // chạy khi editor instance được tạo
+```
+Confirmed: mỗi lần UEditor component mount (tạo editor instance mới),
+tất cả formulas trong document được recalculate lại.
+queueMicrotask đảm bảo chạy sau initial render paint.</t>
+        </is>
+      </c>
+      <c r="J128" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K128" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L128" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M128" s="93" t="inlineStr">
+        <is>
+          <t>Use case quan trọng:
+- Load saved HTML có formula cells → formulas verified khi mount
+- Tránh tình trạng computedValue stale từ lần edit trước
+- Đặc biệt quan trọng khi dùng SSR: immediatelyRender=false
+  (UEditor không render server-side, chỉ render client-side)
+  → mount trigger đảm bảo formula đúng ngay sau hydration</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="120" customHeight="1">
+      <c r="A129" s="82" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C129" s="91" t="inlineStr">
+        <is>
+          <t>TC-T127</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Formula recalculate tự động khi content prop thay đổi từ bên ngoài</t>
+        </is>
+      </c>
+      <c r="E129" s="69" t="inlineStr">
+        <is>
+          <t>Phát hiện từ UEditor.tsx: useEffect([content, editor]) gọi recalculateAllTableFormulas() sau khi setContent() được gọi do content prop thay đổi. Khi parent component thay đổi content prop (load từ API, switch document, undo/redo ngoài editor...), formulas được recalculate lại để đồng bộ với dữ liệu mới.
+lastAppliedContentRef ngăn setContent() không cần thiết khi content không thực sự thay đổi.</t>
+        </is>
+      </c>
+      <c r="F129" s="69" t="inlineStr">
+        <is>
+          <t>Component có state content được control từ bên ngoài (controlled component). Bảng có formula cells. Parent có thể cập nhật content prop.</t>
+        </is>
+      </c>
+      <c r="G129" s="69" t="inlineStr">
+        <is>
+          <t>1. Mount UEditor với content A: bảng A1=10, A2=20, B1='=SUM(A1:A2)'
+2. Verify B1 = 30
+3. Parent thay content prop → content B: bảng A1=100, A2=200, B1='=SUM(A1:A2)'
+4. Quan sát UEditor ngay sau khi content prop change
+5. Verify B1 = 300 (không phải 30 cũ)
+6. Thay content prop lại về content A
+7. Verify B1 = 30 (đúng với A1=10, A2=20)
+8. Đặt cùng content → confirm lastAppliedContentRef ngăn setContent thừa</t>
+        </is>
+      </c>
+      <c r="H129" s="69" t="inlineStr">
+        <is>
+          <t>- Bước 4: B1 cập nhật thành 300 sau khi content prop đổi
+- Bước 7: B1 đúng là 30 khi load lại content A
+- Bước 8: Cùng content không trigger setContent lần 2   (lastAppliedContentRef === newContent → skip)
+- Cơ chế:
+  useEffect([content, editor]) → nếu content khác lastAppliedContentRef
+  → editor.commands.setContent(content)
+  → queueMicrotask → recalculateAllTableFormulas()
+✓ Formula đồng bộ khi content prop thay đổi từ parent</t>
+        </is>
+      </c>
+      <c r="I129" s="69" t="inlineStr">
+        <is>
+          <t>Code trace (UEditor.tsx useEffect content, line 210-230):
+```typescript
+useEffect(() =&gt; {
+  if (!editor || !content) return;
+  if (content === lastAppliedContentRef.current) return;  // anti-loop
+  lastAppliedContentRef.current = content;
+  editor.commands.setContent(content, false);  // setContent
+  queueMicrotask(() =&gt; {
+    if (!editor.isDestroyed) {
+      recalculateAllTableFormulas(editor);  // CONTENT CHANGE TRIGGER
+    }
+  });
+}, [content, editor]);
+```
+lastAppliedContentRef ngăn loop:
+onChange → parent setState → content prop change → useEffect → lastApplied === content → SKIP setContent. Không có vòng lặp.</t>
+        </is>
+      </c>
+      <c r="J129" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K129" s="84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L129" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M129" s="93" t="inlineStr">
+        <is>
+          <t>Quan trọng cho use cases:
+- Collaboration: server push content mới → recalc tự động
+- Multi-document: switch document → formulas của doc mới được recalc
+- Reset: load lại nội dung gốc từ API → formulas luôn đúng
+Lưu ý: lastAppliedContentRef là cơ chế anti-infinite-loop quan trọng.
+Nếu thiếu ref này, onChange → setContent → onChange... vòng lặp vô tận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="120" customHeight="1">
+      <c r="A130" s="87" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C130" s="94" t="inlineStr">
+        <is>
+          <t>TC-T128</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>scheduledFormulaRecalculateRef ngăn cascade recalculation (debounce flag)</t>
+        </is>
+      </c>
+      <c r="E130" s="72" t="inlineStr">
+        <is>
+          <t>Phát hiện từ UEditor.tsx: scheduledFormulaRecalculateRef là boolean ref đóng vai trò debounce flag, ngăn recalculateAllTableFormulas() chạy nhiều lần đồng thời trong cùng một event loop cycle.
+Nếu không có flag này: 1 input event → nhiều onChange transaction → nhiều queueMicrotask → nhiều dispatch gây performance issue.
+Với flag: transaction đầu tiên set flag=true, các transaction tiếp theo trong cùng cycle bị skip. Sau microtask: flag reset về false.</t>
+        </is>
+      </c>
+      <c r="F130" s="72" t="inlineStr">
+        <is>
+          <t>Editor có table với formula. Thực hiện action tạo nhiều ProseMirror transactions liên tiếp (vd: paste nhiều lines, batch format operations).</t>
+        </is>
+      </c>
+      <c r="G130" s="72" t="inlineStr">
+        <is>
+          <t>1. Tạo bảng: A1=1, A2=2, A3=3. B1='=SUM(A1:A3)'
+2. Verify B1 = 6
+3. Paste 3 dòng vào cột A cùng lúc (thay A1=10, A2=20, A3=30)
+4. Quan sát: B1 cập nhật đúng = 60
+5. Mở DevTools Performance tab
+6. Record paste event
+7. Verify: chỉ 1 dispatch cho formula recalculation (không phải 3)
+8. Kiểm tra: RECALCULATE_META=true ngăn loop từ chính recalc dispatch</t>
+        </is>
+      </c>
+      <c r="H130" s="72" t="inlineStr">
+        <is>
+          <t>- B1 cập nhật đúng = 60 sau khi paste
+- Performance: chỉ 1 dispatch (không phải N dispatches)
+  scheduledRef.current=true sau transaction đầu → transactions sau bị skip
+  microtask chạy 1 lần → reset flag → recalculate once
+- RECALCULATE_META check ngăn infinite loop:
+  recalculation dispatch transaction → onUpdate fire lại →   !getMeta(RECALCULATE_META) = false → SKIP → không vòng lặp
+✓ Debounce hoạt động đúng. Chỉ 1 recalculation per event loop cycle.</t>
+        </is>
+      </c>
+      <c r="I130" s="72" t="inlineStr">
+        <is>
+          <t>Code trace (double protection mechanism):
+LAYER 1 - scheduledFormulaRecalculateRef (debounce flag):
+```
+if (!getMeta(RECALCULATE_META) &amp;&amp; !scheduledRef.current) {
+  scheduledRef.current = true;  // SET FLAG
+  queueMicrotask(() =&gt; {
+    scheduledRef.current = false;  // RESET FLAG
+    recalculateAllTableFormulas(editor);
+  });
 }
-editor.view.dispatch(tr.setMeta(..., true));
+// 2nd transaction trong cùng cycle: scheduledRef.current=true → SKIP
 ```
-Confirmed: 1 dispatch, 2 bảng được recalc cùng lúc. Đúng.</t>
-        </is>
-      </c>
-      <c r="J126" s="70" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K126" s="84" t="inlineStr">
+LAYER 2 - RECALCULATE_META (anti-loop):
+```
+// recalculateAllTableFormulas dispatches:
+tr.setMeta(UEDITOR_TABLE_FORMULA_RECALCULATE_META, true)
+// → onUpdate: getMeta(RECALCULATE_META)=true → SKIP scheduling
+// → Không infinite loop
+```
+2 layers bảo vệ: scheduledRef (performance) + META (correctness).</t>
+        </is>
+      </c>
+      <c r="J130" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K130" s="84" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L126" s="89" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M126" s="86" t="inlineStr">
-        <is>
-          <t>recalculateAllTableFormulas() phù hợp khi:
-- Load content (tất cả formulas cần recalc từ đầu)
-- Import/paste nhiều bảng cùng lúc
-- Collaboration: sync formulas sau conflict resolution
-Khác recalculateSelectedTable(): chỉ cần cursor trong bảng.
-UEDITOR_TABLE_FORMULA_SYNC_META (exported nhưng chưa dùng trong package)
-→ reserved cho app-level formula sync handling.</t>
+      <c r="L130" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M130" s="93" t="inlineStr">
+        <is>
+          <t>Cơ chế 2 lớp:
+1. scheduledFormulaRecalculateRef: performance guard
+   → Tối đa 1 recalculation per microtask queue flush
+2. UEDITOR_TABLE_FORMULA_RECALCULATE_META: correctness guard
+   → Recalculation transaction không trigger recalculation mới
+Không cần test regression:
+Nếu thiếu layer 1 → nhiều dispatch, hiệu năng kém
+Nếu thiếu layer 2 → infinite loop crash browser
+Cả 2 layer đều critical.</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9580,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="9">
     <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114 J115 J116 J117 J118 J119 J120 J121 J122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
     </dataValidation>
@@ -9157,6 +9597,15 @@
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
     <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Functional,UI,Edge case"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Functional,UI,Edge case"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/UEditor_Table_TestCase.xlsx
+++ b/docs/UEditor_Table_TestCase.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +161,20 @@
       <color rgb="007C2D12"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -314,6 +326,11 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -341,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -597,6 +614,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -964,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6982,10 +7017,13 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M94" s="81" t="inlineStr">
+      <c r="M94" s="95" t="inlineStr">
         <is>
           <t>✓ Normalize đúng.
-ℹ UEDITOR_TABLE_FORMULA_SYNC_META = 'ueditorTableFormulaSync' được export từ table-formula-commands.ts nhưng chưa sử dụng trong package. Đây là meta key dành cho consumer (app/plugin) detect formula sync transaction. Cần document trong API docs.</t>
+✅ FIX (2026-06-07): UEDITOR_TABLE_FORMULA_SYNC_META đã được xóa khỏi package.
+Trước đây: export const UEDITOR_TABLE_FORMULA_SYNC_META = 'ueditorTableFormulaSync' tồn tại trong table-formula-commands.ts nhưng không dùng trong package.
+Sau fix: export bị loại bỏ hoàn toàn. API surface gọn hơn.
+npm run typecheck: pass sau khi xóa.</t>
         </is>
       </c>
     </row>
@@ -9161,17 +9199,16 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M126" s="90" t="inlineStr">
-        <is>
-          <t>⚠ PHÁT HIỆN QUAN TRỌNG (từ UEditor.tsx):
-recalculateAllTableFormulas() KHÔNG phải manual API call mà được gọi TỰ ĐỘNG:
-1. onUpdate: mỗi editor change → queueMicrotask → recalculateAllTableFormulas()
-   (chống cascade bằng scheduledFormulaRecalculateRef)
-2. useEffect([editor]): gọi khi editor mount
-3. useEffect([content, editor]): gọi khi content prop thay đổi
-→ Test thực tế: KHÔNG cần gọi manual API.
-Chỉ cần thay đổi data trong table → formulas tự recalc tức thì.
-Xem TC-T125, TC-T126, TC-T127, TC-T128 để test chi tiết từng trigger.</t>
+      <c r="M126" s="96" t="inlineStr">
+        <is>
+          <t>recalculateAllTableFormulas() phù hợp khi:
+- Load content (tất cả formulas cần recalc từ đầu)
+- Import/paste nhiều bảng cùng lúc
+- Collaboration: sync formulas sau conflict resolution
+Khác recalculateSelectedTable(): chỉ cần cursor trong bảng.
+✅ FIX (2026-06-07): UEDITOR_TABLE_FORMULA_SYNC_META đã bị xóa khỏi package.
+Chỉ còn UEDITOR_TABLE_FORMULA_RECALCULATE_META (dùng để ngăn infinite loop).
+Xem TC-T092 ghi chú chi tiết về việc xóa SYNC_META.</t>
         </is>
       </c>
     </row>
@@ -9576,11 +9613,311 @@
         </is>
       </c>
     </row>
+    <row r="131" ht="115" customHeight="1">
+      <c r="A131" s="82" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C131" s="97" t="inlineStr">
+        <is>
+          <t>TC-T129</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>formatTableFormulaDisplayValue — hiển thị computed value theo numberFormat của cell</t>
+        </is>
+      </c>
+      <c r="E131" s="69" t="inlineStr">
+        <is>
+          <t>Thêm mới (2026-06-07): formatTableFormulaDisplayValue(value, numberFormat) được gọi trong recalculateTableNode() để format display content của formula cell.
+Tách biệt hai khái niệm:
+• computedValue attr = raw numeric string (ví dụ '1234.5') — dùng cho formula dependency
+• Cell display content = formatTableFormulaDisplayValue(computedValue, numberFormat) — dùng để hiển thị cho user
+numberFormat: 'text' | 'number' | 'currency' | 'percent' | 'date'
+Default ('text'): không format, hiển thị raw value.</t>
+        </is>
+      </c>
+      <c r="F131" s="69" t="inlineStr">
+        <is>
+          <t>Bảng 2×2. A1=1234.5 (số). B1 có formula '=A1'.
+Thử các giá trị numberFormat khác nhau trên B1 (qua attrs hoặc UI).</t>
+        </is>
+      </c>
+      <c r="G131" s="69" t="inlineStr">
+        <is>
+          <t>1. Bảng: A1='1234.5', B1 formula '=A1'
+2. numberFormat='text' (mặc định) → quan sát B1
+3. numberFormat='number' → quan sát B1
+4. numberFormat='currency' → quan sát B1
+5. numberFormat='percent' → quan sát B1 (A1='0.125' để test)
+6. numberFormat='date' → quan sát B1 (A1='45658' để test)
+7. Formula trả về error (#INVALID-REFERENCE) + numberFormat='currency' → quan sát
+8. Kiểm tra data-computed-value trong DOM (phải là raw value)</t>
+        </is>
+      </c>
+      <c r="H131" s="69" t="inlineStr">
+        <is>
+          <t>1. numberFormat='text': B1 hiển thị '1234.5' (raw)
+2. numberFormat='number': B1 hiển thị '1,234.5' (Intl.NumberFormat en-US)
+3. numberFormat='currency': B1 hiển thị '$1,234.50' (USD, 2 decimal)
+4. numberFormat='percent': A1='0.125' → B1 hiển thị '12.5%'
+5. numberFormat='date': A1='45658' → B1 hiển thị '01/01/2025'
+   (45658 ngày từ Excel epoch 1899-12-30 = 2025-01-01)
+6. Error pass-through: '#INVALID-REFERENCE' + currency → hiển thị '#INVALID-REFERENCE'
+   (stringValue.startsWith('#') → return as-is)
+7. DOM: data-computed-value='1234.5' (raw), cell text = '$1,234.50' (formatted)
+   → computedValue phục vụ formula dependency, display phục vụ UX</t>
+        </is>
+      </c>
+      <c r="I131" s="69" t="inlineStr">
+        <is>
+          <t>Code trace (table-formula.ts + table-formula-commands.ts):
+formatTableFormulaDisplayValue(value, numberFormat):
+  if startsWith('#') → return as-is (error pass-through)
+  if 'text' → return String(value)
+  numericValue = parseFloat(value)
+  if !isFinite → return String(value) (non-numeric fallback)
+  'number' → Intl.NumberFormat('en-US', {maxFractionDigits:6}).format(n)
+  'currency' → Intl.NumberFormat('en-US', {style:'currency',currency:'USD',maxFractionDigits:2})
+  'percent' → Intl.NumberFormat('en-US', {style:'percent',maxFractionDigits:2})
+  'date' → epoch = Date.UTC(1899,11,30) + n*86400000
+           → Intl.DateTimeFormat('en-US', {year,month,day,timeZone:'UTC'})
+Unit test (ueditor-table-formula.test.mjs) xác nhận:
+  formatTableFormulaDisplayValue('1234.5', 'number') = '1,234.5'
+  formatTableFormulaDisplayValue('1234.5', 'currency') = '$1,234.50'
+  formatTableFormulaDisplayValue('0.125', 'percent') = '12.5%'
+  formatTableFormulaDisplayValue('45658', 'date') = '01/01/2025'
+  formatTableFormulaDisplayValue('#INVALID-REFERENCE', 'currency') = '#INVALID-REFERENCE'</t>
+        </is>
+      </c>
+      <c r="J131" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K131" s="92" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L131" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M131" s="98" t="inlineStr">
+        <is>
+          <t>Thiết kế quan trọng:
+computedValue (raw) ≠ display content (formatted)
+→ Formula dependency dùng raw, người dùng thấy formatted.
+Unit test đã lock behavior trong:
+packages/underverse/tests/ueditor-table-formula.test.mjs
+'UEditor table formula utilities format computed display values'
+Locale: 'en-US' hardcoded → '$1,234.50' không phải '1.234,50'.
+Nếu cần i18n, cần cập nhật hàm để nhận locale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="115" customHeight="1">
+      <c r="A132" s="87" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C132" s="99" t="inlineStr">
+        <is>
+          <t>TC-T130</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>computedValue attr giữ raw value — display content được format theo numberFormat</t>
+        </is>
+      </c>
+      <c r="E132" s="72" t="inlineStr">
+        <is>
+          <t>Kiểm tra tính tách biệt giữa data layer và display layer:
+• computedValue attr (data-computed-value trong DOM) = raw numeric string
+• Cell content text = formatTableFormulaDisplayValue(computedValue, numberFormat)
+Khi cell B2 tham chiếu B1 (formula cell có numberFormat='currency'):
+B2 phải dùng raw value từ computedValue của B1, không phải display '$1,234.50'.</t>
+        </is>
+      </c>
+      <c r="F132" s="72" t="inlineStr">
+        <is>
+          <t>Bảng 3 hàng. A1=1000. B1 formula '=A1', numberFormat='currency'. B2 formula '=B1*2' (tham chiếu B1 formatted).</t>
+        </is>
+      </c>
+      <c r="G132" s="72" t="inlineStr">
+        <is>
+          <t>1. A1=1000, B1='=A1' với numberFormat='currency'
+2. Verify B1 display = '$1,000.00', data-computed-value='1000'
+3. B2='=B1*2'
+4. Quan sát B2
+5. Kiểm tra DOM: data-computed-value của B2
+6. Đổi A1=2000 → quan sát B1 và B2 update đồng bộ</t>
+        </is>
+      </c>
+      <c r="H132" s="72" t="inlineStr">
+        <is>
+          <t>- B1 display = '$1,000.00', data-computed-value = '1000'
+- B2 = '=B1*2': getCellValue('B1') trả '1000' (từ computedValue raw)
+  → 1000 * 2 = 2000 → B2 data-computed-value = '2000'
+  → B2 display (numberFormat='text' mặc định) = '2000'
+- Sau A1=2000: B1 = '$2,000.00', B2 = '4000'
+✓ Formula chain dùng raw values, không bị lẫn formatted strings.
+✓ '$1,000.00' không được parseFloat là 1000 (dấu '$' gây NaN),
+  nhưng không sao vì getCellValue() lấy từ computedValue attr = '1000'.</t>
+        </is>
+      </c>
+      <c r="I132" s="72" t="inlineStr">
+        <is>
+          <t>Code trace (recalculateTableNode + buildTableValueMap):
+buildTableValueMap() (dùng cho getCellValue):
+  const computedValue = entry.node.attrs.computedValue;
+  values.set(label, computedValue.trim() ? computedValue : getCellText(entry.node));
+  → Luôn dùng raw computedValue, không bao giờ dùng display text.
+recalculateTableNode():
+  computedValue = String(result.value)          // raw '1000'
+  displayValue = formatTableFormulaDisplayValue(computedValue, numberFormat) // '$1,000.00'
+  cell.attrs.computedValue = computedValue      // raw
+  cell content = createCellDisplayContent(displayValue) // formatted
+→ data layer (computedValue) và display layer tách biệt hoàn toàn.</t>
+        </is>
+      </c>
+      <c r="J132" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K132" s="92" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L132" s="89" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M132" s="98" t="inlineStr">
+        <is>
+          <t>Invariant quan trọng:
+getCellValue() luôn đọc attrs.computedValue (raw), không đọc DOM text.
+→ Formatting không ảnh hưởng đến formula dependency chain.
+Nếu vi phạm invariant này: SUM($1,000.00:$2,000.00) → parseFloat('$1,000.00') = NaN → #INVALID-REFERENCE.
+Hiện tại code đúng: buildTableValueMap dùng attrs.computedValue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="115" customHeight="1">
+      <c r="A133" s="82" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="27" t="inlineStr">
+        <is>
+          <t>11. Formula (Công thức)</t>
+        </is>
+      </c>
+      <c r="C133" s="97" t="inlineStr">
+        <is>
+          <t>TC-T131</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>normalizeTableNumberFormat — validate và fallback về 'text' cho format không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E133" s="69" t="inlineStr">
+        <is>
+          <t>normalizeTableNumberFormat(format) validate giá trị numberFormat attr.
+Chỉ chấp nhận: 'text' | 'number' | 'currency' | 'percent' | 'date'.
+Mọi giá trị khác (null, undefined, '', 'foo', số) → fallback về 'text'.
+Hàm này được gọi trong formatTableFormulaDisplayValue() trước khi format.</t>
+        </is>
+      </c>
+      <c r="F133" s="69" t="inlineStr">
+        <is>
+          <t>Formula cell với numberFormat attr được set các giá trị khác nhau.</t>
+        </is>
+      </c>
+      <c r="G133" s="69" t="inlineStr">
+        <is>
+          <t>1. numberFormat='text' → normalizeTableNumberFormat trả 'text'
+2. numberFormat='number' → trả 'number'
+3. numberFormat='currency' → trả 'currency'
+4. numberFormat='percent' → trả 'percent'
+5. numberFormat='date' → trả 'date'
+6. numberFormat=null → trả 'text' (fallback)
+7. numberFormat=undefined → trả 'text'
+8. numberFormat='invalid' → trả 'text'
+9. numberFormat=123 (số) → trả 'text'
+10. numberFormat='' → trả 'text'</t>
+        </is>
+      </c>
+      <c r="H133" s="69" t="inlineStr">
+        <is>
+          <t>- Các giá trị hợp lệ ('text','number','currency','percent','date') → trả đúng
+- Mọi giá trị không hợp lệ → fallback 'text' → display raw value
+- Không throw error với bất kỳ input nào
+- formatTableFormulaDisplayValue với format không hợp lệ: display raw string
+✓ Defensive programming: cell attrs corrupt không gây crash</t>
+        </is>
+      </c>
+      <c r="I133" s="69" t="inlineStr">
+        <is>
+          <t>Code trace (table-formula.ts):
+export type TableNumberFormat = 'text' | 'number' | 'currency' | 'percent' | 'date';
+export function normalizeTableNumberFormat(format: unknown): TableNumberFormat {
+  return format === 'text' || format === 'number' || format === 'currency'
+      || format === 'percent' || format === 'date'
+    ? format
+    : 'text';  // fallback cho mọi giá trị khác
+}
+Trong formatTableFormulaDisplayValue():
+  const normalizedFormat = normalizeTableNumberFormat(numberFormat);
+  if (normalizedFormat === 'text') return stringValue;
+  // ... format theo normalized value
+Unit tests pass xác nhận behavior đúng.</t>
+        </is>
+      </c>
+      <c r="J133" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K133" s="100" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L133" s="85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M133" s="98" t="inlineStr">
+        <is>
+          <t>Defensive: attrs từ paste/import HTML có thể có giá trị bất kỳ.
+normalizeTableNumberFormat đảm bảo không crash với input bất thường.
+Default 'text' là safe choice: hiển thị raw value, không mất thông tin.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="12">
     <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114 J115 J116 J117 J118 J119 J120 J121 J122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
     </dataValidation>
@@ -9608,6 +9945,15 @@
     <dataValidation sqref="L3:L600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Functional,UI,Edge case"</formula1>
     </dataValidation>
+    <dataValidation sqref="J3:J700" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Chưa test,Pass,Fail,Blocked,Re-test,Fixed,Skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K700" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L700" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Functional,UI,Edge case"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/UEditor_Table_TestCase.xlsx
+++ b/docs/UEditor_Table_TestCase.xlsx
@@ -1397,12 +1397,12 @@
       </c>
       <c r="I7" s="69" t="inlineStr">
         <is>
-          <t>Demo không bật showMenuBar=true. Không có menu bar. Không test được Insert &gt; Table từ menu bar.</t>
+          <t>showMenuBar=true đã được cấu hình trong Menu Bar editor của UEditorExample.tsx. Menu Bar hiển thị đủ 7 menu: Tập tin, Sửa, Xem, Thêm, Định dạng, Công cụ, Bảng. Click Bảng &gt; Insert Table → bảng được tạo trong editor.</t>
         </is>
       </c>
       <c r="J7" s="74" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="M7" s="75" t="inlineStr">
         <is>
-          <t>Cần showMenuBar=true</t>
+          <t>showMenuBar đã có sẵn trong Menu Bar editor của UEditorExample.tsx từ trước. TC có thể test được.</t>
         </is>
       </c>
     </row>
